--- a/artfynd/A 2227-2024 artfynd.xlsx
+++ b/artfynd/A 2227-2024 artfynd.xlsx
@@ -2464,10 +2464,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118376493</v>
+        <v>118374544</v>
       </c>
       <c r="B17" t="n">
-        <v>78484</v>
+        <v>97763</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2476,30 +2476,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2507,10 +2520,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>529564</v>
+        <v>529757</v>
       </c>
       <c r="R17" t="n">
-        <v>7168298</v>
+        <v>7168700</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2545,6 +2558,11 @@
           <t>2024-07-10</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>utan fläckar på bladen</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2557,7 +2575,7 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
+          <t>Blandsumpskog</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2575,10 +2593,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118374544</v>
+        <v>118377198</v>
       </c>
       <c r="B18" t="n">
-        <v>97763</v>
+        <v>98180</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2591,26 +2609,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219790</v>
+        <v>219880</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2620,7 +2638,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
@@ -2631,10 +2649,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>529757</v>
+        <v>529781</v>
       </c>
       <c r="R18" t="n">
-        <v>7168700</v>
+        <v>7168708</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2667,11 +2685,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-07-10</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>utan fläckar på bladen</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2704,10 +2717,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118377198</v>
+        <v>118376493</v>
       </c>
       <c r="B19" t="n">
-        <v>98180</v>
+        <v>78484</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2716,43 +2729,30 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219880</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2760,10 +2760,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>529781</v>
+        <v>529564</v>
       </c>
       <c r="R19" t="n">
-        <v>7168708</v>
+        <v>7168298</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>Blandsumpskog</t>
+          <t>Blåbärsblandskog</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3416,10 +3416,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118374825</v>
+        <v>118377613</v>
       </c>
       <c r="B25" t="n">
-        <v>78484</v>
+        <v>79601</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3428,25 +3428,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3459,10 +3459,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>529615</v>
+        <v>529724</v>
       </c>
       <c r="R25" t="n">
-        <v>7168654</v>
+        <v>7168444</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3509,7 +3509,27 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>Högörtblandskog</t>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3527,10 +3547,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118376619</v>
+        <v>118377497</v>
       </c>
       <c r="B26" t="n">
-        <v>78484</v>
+        <v>79601</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3539,25 +3559,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3570,10 +3590,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>529335</v>
+        <v>529366</v>
       </c>
       <c r="R26" t="n">
-        <v>7168411</v>
+        <v>7168437</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3621,6 +3641,26 @@
       <c r="AH26" t="inlineStr">
         <is>
           <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3638,10 +3678,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118377613</v>
+        <v>118374825</v>
       </c>
       <c r="B27" t="n">
-        <v>79601</v>
+        <v>78484</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3650,25 +3690,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3681,10 +3721,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>529724</v>
+        <v>529615</v>
       </c>
       <c r="R27" t="n">
-        <v>7168444</v>
+        <v>7168654</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3731,27 +3771,7 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Högörtblandskog</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3769,10 +3789,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118377497</v>
+        <v>118376619</v>
       </c>
       <c r="B28" t="n">
-        <v>79601</v>
+        <v>78484</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3781,25 +3801,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3812,10 +3832,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>529366</v>
+        <v>529335</v>
       </c>
       <c r="R28" t="n">
-        <v>7168437</v>
+        <v>7168411</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3863,26 +3883,6 @@
       <c r="AH28" t="inlineStr">
         <is>
           <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3900,10 +3900,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118376507</v>
+        <v>118373894</v>
       </c>
       <c r="B29" t="n">
-        <v>78484</v>
+        <v>97763</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3912,30 +3912,43 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3943,10 +3956,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>529596</v>
+        <v>529729</v>
       </c>
       <c r="R29" t="n">
-        <v>7168313</v>
+        <v>7168738</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3993,7 +4006,7 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
+          <t>Blandsumpskog</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4011,10 +4024,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118373894</v>
+        <v>118376507</v>
       </c>
       <c r="B30" t="n">
-        <v>97763</v>
+        <v>78484</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4023,43 +4036,30 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4067,10 +4067,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>529729</v>
+        <v>529596</v>
       </c>
       <c r="R30" t="n">
-        <v>7168738</v>
+        <v>7168313</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -4117,7 +4117,7 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Blandsumpskog</t>
+          <t>Blåbärsblandskog</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -5756,10 +5756,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118638347</v>
+        <v>118640655</v>
       </c>
       <c r="B44" t="n">
-        <v>79601</v>
+        <v>104925</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5772,26 +5772,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6464</v>
+        <v>221725</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5799,10 +5812,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>529581</v>
+        <v>529831</v>
       </c>
       <c r="R44" t="n">
-        <v>7168387</v>
+        <v>7168496</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5849,27 +5862,7 @@
       </c>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Högörtblandskog</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5887,10 +5880,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118640485</v>
+        <v>118638347</v>
       </c>
       <c r="B45" t="n">
-        <v>104925</v>
+        <v>79601</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5903,39 +5896,26 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221725</v>
+        <v>6464</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr"/>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5943,10 +5923,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>529812</v>
+        <v>529581</v>
       </c>
       <c r="R45" t="n">
-        <v>7168477</v>
+        <v>7168387</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5993,7 +5973,27 @@
       </c>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>Högörtblandskog</t>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6011,7 +6011,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118640655</v>
+        <v>118640485</v>
       </c>
       <c r="B46" t="n">
         <v>104925</v>
@@ -6067,10 +6067,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>529831</v>
+        <v>529812</v>
       </c>
       <c r="R46" t="n">
-        <v>7168496</v>
+        <v>7168477</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>

--- a/artfynd/A 2227-2024 artfynd.xlsx
+++ b/artfynd/A 2227-2024 artfynd.xlsx
@@ -1393,10 +1393,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118376570</v>
+        <v>118372729</v>
       </c>
       <c r="B8" t="n">
-        <v>78484</v>
+        <v>97763</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1405,30 +1405,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1436,10 +1449,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>529817</v>
+        <v>529835</v>
       </c>
       <c r="R8" t="n">
-        <v>7168518</v>
+        <v>7168557</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1504,10 +1517,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118376237</v>
+        <v>118376886</v>
       </c>
       <c r="B9" t="n">
-        <v>78484</v>
+        <v>98180</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1516,30 +1529,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>219880</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1547,10 +1573,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>529559</v>
+        <v>529825</v>
       </c>
       <c r="R9" t="n">
-        <v>7168596</v>
+        <v>7168680</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1597,7 +1623,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
+          <t>Blandsumpskog</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1615,10 +1641,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118372729</v>
+        <v>118376570</v>
       </c>
       <c r="B10" t="n">
-        <v>97763</v>
+        <v>78484</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1627,43 +1653,30 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1671,10 +1684,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>529835</v>
+        <v>529817</v>
       </c>
       <c r="R10" t="n">
-        <v>7168557</v>
+        <v>7168518</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1739,10 +1752,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118376886</v>
+        <v>118376237</v>
       </c>
       <c r="B11" t="n">
-        <v>98180</v>
+        <v>78484</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1751,43 +1764,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219880</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1795,10 +1795,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>529825</v>
+        <v>529559</v>
       </c>
       <c r="R11" t="n">
-        <v>7168680</v>
+        <v>7168596</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1845,7 +1845,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Blandsumpskog</t>
+          <t>Blåbärsblandskog</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2464,10 +2464,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118374544</v>
+        <v>118376493</v>
       </c>
       <c r="B17" t="n">
-        <v>97763</v>
+        <v>78484</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2476,43 +2476,30 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2520,10 +2507,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>529757</v>
+        <v>529564</v>
       </c>
       <c r="R17" t="n">
-        <v>7168700</v>
+        <v>7168298</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2558,11 +2545,6 @@
           <t>2024-07-10</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>utan fläckar på bladen</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2575,7 +2557,7 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Blandsumpskog</t>
+          <t>Blåbärsblandskog</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2593,10 +2575,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118377198</v>
+        <v>118374544</v>
       </c>
       <c r="B18" t="n">
-        <v>98180</v>
+        <v>97763</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2609,26 +2591,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219880</v>
+        <v>219790</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>37</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2638,7 +2620,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
@@ -2649,10 +2631,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>529781</v>
+        <v>529757</v>
       </c>
       <c r="R18" t="n">
-        <v>7168708</v>
+        <v>7168700</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2685,6 +2667,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-07-10</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>utan fläckar på bladen</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2717,10 +2704,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118376493</v>
+        <v>118377198</v>
       </c>
       <c r="B19" t="n">
-        <v>78484</v>
+        <v>98180</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2729,30 +2716,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>219880</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2760,10 +2760,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>529564</v>
+        <v>529781</v>
       </c>
       <c r="R19" t="n">
-        <v>7168298</v>
+        <v>7168708</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
+          <t>Blandsumpskog</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>

--- a/artfynd/A 2227-2024 artfynd.xlsx
+++ b/artfynd/A 2227-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118376553</v>
+        <v>118377115</v>
       </c>
       <c r="B2" t="n">
-        <v>78484</v>
+        <v>98180</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>219880</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +731,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>529742</v>
+        <v>529828</v>
       </c>
       <c r="R2" t="n">
-        <v>7168447</v>
+        <v>7168693</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -786,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118374116</v>
+        <v>118377695</v>
       </c>
       <c r="B3" t="n">
-        <v>97763</v>
+        <v>79601</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,39 +815,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>6464</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>529691</v>
+        <v>529416</v>
       </c>
       <c r="R3" t="n">
-        <v>7168682</v>
+        <v>7168380</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -892,7 +892,27 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Blandsumpskog</t>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -910,10 +930,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118376653</v>
+        <v>118377198</v>
       </c>
       <c r="B4" t="n">
-        <v>104925</v>
+        <v>98180</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,26 +946,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221725</v>
+        <v>219880</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -955,7 +975,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
@@ -966,10 +986,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>529335</v>
+        <v>529781</v>
       </c>
       <c r="R4" t="n">
-        <v>7168411</v>
+        <v>7168708</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1016,7 +1036,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
+          <t>Blandsumpskog</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1158,10 +1178,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118376316</v>
+        <v>118376653</v>
       </c>
       <c r="B6" t="n">
-        <v>78484</v>
+        <v>104925</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1170,30 +1190,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>221725</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1201,10 +1234,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>529455</v>
+        <v>529335</v>
       </c>
       <c r="R6" t="n">
-        <v>7168453</v>
+        <v>7168411</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1269,10 +1302,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118374236</v>
+        <v>118376507</v>
       </c>
       <c r="B7" t="n">
-        <v>97867</v>
+        <v>78484</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1281,43 +1314,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1325,10 +1345,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>529691</v>
+        <v>529596</v>
       </c>
       <c r="R7" t="n">
-        <v>7168682</v>
+        <v>7168313</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1375,7 +1395,7 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Blandsumpskog</t>
+          <t>Blåbärsblandskog</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1517,10 +1537,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118376886</v>
+        <v>118372553</v>
       </c>
       <c r="B9" t="n">
-        <v>98180</v>
+        <v>97763</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1533,26 +1553,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219880</v>
+        <v>219790</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1562,7 +1582,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
@@ -1573,10 +1593,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>529825</v>
+        <v>529778</v>
       </c>
       <c r="R9" t="n">
-        <v>7168680</v>
+        <v>7168467</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1641,10 +1661,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118376570</v>
+        <v>118374393</v>
       </c>
       <c r="B10" t="n">
-        <v>78484</v>
+        <v>97763</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1653,30 +1673,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1684,10 +1717,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>529817</v>
+        <v>529828</v>
       </c>
       <c r="R10" t="n">
-        <v>7168518</v>
+        <v>7168707</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1720,6 +1753,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-07-10</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>mer eller mindre fläckiga blad</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1752,10 +1790,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118376237</v>
+        <v>118377497</v>
       </c>
       <c r="B11" t="n">
-        <v>78484</v>
+        <v>79601</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1764,25 +1802,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1795,10 +1833,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>529559</v>
+        <v>529366</v>
       </c>
       <c r="R11" t="n">
-        <v>7168596</v>
+        <v>7168437</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1846,6 +1884,26 @@
       <c r="AH11" t="inlineStr">
         <is>
           <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1863,10 +1921,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118373653</v>
+        <v>118377613</v>
       </c>
       <c r="B12" t="n">
-        <v>97763</v>
+        <v>79601</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1879,39 +1937,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219790</v>
+        <v>6464</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1919,10 +1964,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>529821</v>
+        <v>529724</v>
       </c>
       <c r="R12" t="n">
-        <v>7168618</v>
+        <v>7168444</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1957,11 +2002,6 @@
           <t>2024-07-10</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>stort område med tät förekomst. Många med blad utan fläckar.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1971,6 +2011,31 @@
       <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2098,10 +2163,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118372553</v>
+        <v>118374825</v>
       </c>
       <c r="B14" t="n">
-        <v>97763</v>
+        <v>78484</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2110,43 +2175,30 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2154,10 +2206,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>529778</v>
+        <v>529615</v>
       </c>
       <c r="R14" t="n">
-        <v>7168467</v>
+        <v>7168654</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2204,7 +2256,7 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Blandsumpskog</t>
+          <t>Högörtblandskog</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2222,7 +2274,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118374787</v>
+        <v>118376493</v>
       </c>
       <c r="B15" t="n">
         <v>78484</v>
@@ -2265,10 +2317,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>529672</v>
+        <v>529564</v>
       </c>
       <c r="R15" t="n">
-        <v>7168655</v>
+        <v>7168298</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2315,7 +2367,7 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Högörtblandskog</t>
+          <t>Blåbärsblandskog</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2333,10 +2385,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118377695</v>
+        <v>118376346</v>
       </c>
       <c r="B16" t="n">
-        <v>79601</v>
+        <v>78484</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2345,25 +2397,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2376,10 +2428,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>529416</v>
+        <v>529375</v>
       </c>
       <c r="R16" t="n">
-        <v>7168380</v>
+        <v>7168391</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2427,26 +2479,6 @@
       <c r="AH16" t="inlineStr">
         <is>
           <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2464,7 +2496,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118376493</v>
+        <v>118376316</v>
       </c>
       <c r="B17" t="n">
         <v>78484</v>
@@ -2507,10 +2539,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>529564</v>
+        <v>529455</v>
       </c>
       <c r="R17" t="n">
-        <v>7168298</v>
+        <v>7168453</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2575,10 +2607,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118374544</v>
+        <v>118374236</v>
       </c>
       <c r="B18" t="n">
-        <v>97763</v>
+        <v>97867</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2591,26 +2623,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219790</v>
+        <v>221952</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2631,10 +2663,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>529757</v>
+        <v>529691</v>
       </c>
       <c r="R18" t="n">
-        <v>7168700</v>
+        <v>7168682</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2667,11 +2699,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-07-10</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>utan fläckar på bladen</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2704,10 +2731,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118377198</v>
+        <v>118374116</v>
       </c>
       <c r="B19" t="n">
-        <v>98180</v>
+        <v>97763</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2720,26 +2747,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219880</v>
+        <v>219790</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2749,7 +2776,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
@@ -2760,10 +2787,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>529781</v>
+        <v>529691</v>
       </c>
       <c r="R19" t="n">
-        <v>7168708</v>
+        <v>7168682</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2828,10 +2855,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118373990</v>
+        <v>118373894</v>
       </c>
       <c r="B20" t="n">
-        <v>78484</v>
+        <v>97763</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2840,30 +2867,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2939,10 +2979,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118377115</v>
+        <v>118374699</v>
       </c>
       <c r="B21" t="n">
-        <v>98180</v>
+        <v>78484</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2951,43 +2991,30 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219880</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2995,10 +3022,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>529828</v>
+        <v>529749</v>
       </c>
       <c r="R21" t="n">
-        <v>7168693</v>
+        <v>7168733</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -3063,10 +3090,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118377821</v>
+        <v>118373990</v>
       </c>
       <c r="B22" t="n">
-        <v>79601</v>
+        <v>78484</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3075,25 +3102,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3106,10 +3133,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>529473</v>
+        <v>529729</v>
       </c>
       <c r="R22" t="n">
-        <v>7168495</v>
+        <v>7168738</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3156,27 +3183,7 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Blandsumpskog</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3194,7 +3201,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118376346</v>
+        <v>118376553</v>
       </c>
       <c r="B23" t="n">
         <v>78484</v>
@@ -3237,10 +3244,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>529375</v>
+        <v>529742</v>
       </c>
       <c r="R23" t="n">
-        <v>7168391</v>
+        <v>7168447</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3287,7 +3294,7 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
+          <t>Blandsumpskog</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3305,7 +3312,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118376431</v>
+        <v>118374787</v>
       </c>
       <c r="B24" t="n">
         <v>78484</v>
@@ -3348,10 +3355,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>529430</v>
+        <v>529672</v>
       </c>
       <c r="R24" t="n">
-        <v>7168343</v>
+        <v>7168655</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3398,7 +3405,7 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
+          <t>Högörtblandskog</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3416,10 +3423,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118377613</v>
+        <v>118376570</v>
       </c>
       <c r="B25" t="n">
-        <v>79601</v>
+        <v>78484</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3428,25 +3435,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3459,10 +3466,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>529724</v>
+        <v>529817</v>
       </c>
       <c r="R25" t="n">
-        <v>7168444</v>
+        <v>7168518</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3509,27 +3516,7 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Blandsumpskog</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3547,10 +3534,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118377497</v>
+        <v>118374544</v>
       </c>
       <c r="B26" t="n">
-        <v>79601</v>
+        <v>97763</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3563,26 +3550,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6464</v>
+        <v>219790</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3590,10 +3590,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>529366</v>
+        <v>529757</v>
       </c>
       <c r="R26" t="n">
-        <v>7168437</v>
+        <v>7168700</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3628,6 +3628,11 @@
           <t>2024-07-10</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>utan fläckar på bladen</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3640,27 +3645,7 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Blandsumpskog</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3678,10 +3663,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118374825</v>
+        <v>118376886</v>
       </c>
       <c r="B27" t="n">
-        <v>78484</v>
+        <v>98180</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3690,30 +3675,43 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>219880</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3721,10 +3719,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>529615</v>
+        <v>529825</v>
       </c>
       <c r="R27" t="n">
-        <v>7168654</v>
+        <v>7168680</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3771,7 +3769,7 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Högörtblandskog</t>
+          <t>Blandsumpskog</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3789,10 +3787,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118376619</v>
+        <v>118373653</v>
       </c>
       <c r="B28" t="n">
-        <v>78484</v>
+        <v>97763</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3801,30 +3799,43 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3832,10 +3843,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>529335</v>
+        <v>529821</v>
       </c>
       <c r="R28" t="n">
-        <v>7168411</v>
+        <v>7168618</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3870,6 +3881,11 @@
           <t>2024-07-10</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>stort område med tät förekomst. Många med blad utan fläckar.</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3879,11 +3895,6 @@
       <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3900,10 +3911,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118373894</v>
+        <v>118377821</v>
       </c>
       <c r="B29" t="n">
-        <v>97763</v>
+        <v>79601</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3916,39 +3927,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219790</v>
+        <v>6464</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr"/>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3956,10 +3954,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>529729</v>
+        <v>529473</v>
       </c>
       <c r="R29" t="n">
-        <v>7168738</v>
+        <v>7168495</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -4006,7 +4004,27 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Blandsumpskog</t>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4024,7 +4042,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118376507</v>
+        <v>118376431</v>
       </c>
       <c r="B30" t="n">
         <v>78484</v>
@@ -4067,10 +4085,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>529596</v>
+        <v>529430</v>
       </c>
       <c r="R30" t="n">
-        <v>7168313</v>
+        <v>7168343</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -4135,7 +4153,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118374699</v>
+        <v>118376521</v>
       </c>
       <c r="B31" t="n">
         <v>78484</v>
@@ -4178,10 +4196,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>529749</v>
+        <v>529657</v>
       </c>
       <c r="R31" t="n">
-        <v>7168733</v>
+        <v>7168427</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4228,7 +4246,7 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Blandsumpskog</t>
+          <t>Blåbärsblandskog</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4246,7 +4264,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118376521</v>
+        <v>118376237</v>
       </c>
       <c r="B32" t="n">
         <v>78484</v>
@@ -4289,10 +4307,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>529657</v>
+        <v>529559</v>
       </c>
       <c r="R32" t="n">
-        <v>7168427</v>
+        <v>7168596</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4357,10 +4375,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118374393</v>
+        <v>118376619</v>
       </c>
       <c r="B33" t="n">
-        <v>97763</v>
+        <v>78484</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4369,43 +4387,30 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4413,10 +4418,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>529828</v>
+        <v>529335</v>
       </c>
       <c r="R33" t="n">
-        <v>7168707</v>
+        <v>7168411</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4451,11 +4456,6 @@
           <t>2024-07-10</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>mer eller mindre fläckiga blad</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>Blandsumpskog</t>
+          <t>Blåbärsblandskog</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4486,7 +4486,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118638030</v>
+        <v>118638347</v>
       </c>
       <c r="B34" t="n">
         <v>79601</v>
@@ -4529,10 +4529,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>529474</v>
+        <v>529581</v>
       </c>
       <c r="R34" t="n">
-        <v>7168472</v>
+        <v>7168387</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4617,10 +4617,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118638559</v>
+        <v>118639270</v>
       </c>
       <c r="B35" t="n">
-        <v>78484</v>
+        <v>79594</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4629,25 +4629,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4660,10 +4660,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>529439</v>
+        <v>529596</v>
       </c>
       <c r="R35" t="n">
-        <v>7168447</v>
+        <v>7168627</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4711,26 +4711,6 @@
       <c r="AH35" t="inlineStr">
         <is>
           <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4748,7 +4728,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118637596</v>
+        <v>118638521</v>
       </c>
       <c r="B36" t="n">
         <v>78484</v>
@@ -4791,10 +4771,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>529657</v>
+        <v>529374</v>
       </c>
       <c r="R36" t="n">
-        <v>7168658</v>
+        <v>7168443</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4841,7 +4821,7 @@
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>Högörtblandskog</t>
+          <t>Blåbärsblandskog</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4859,7 +4839,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118637579</v>
+        <v>118638579</v>
       </c>
       <c r="B37" t="n">
         <v>79601</v>
@@ -4902,10 +4882,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>529657</v>
+        <v>529439</v>
       </c>
       <c r="R37" t="n">
-        <v>7168658</v>
+        <v>7168447</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4949,31 +4929,6 @@
       <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>Högörtblandskog</t>
-        </is>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4990,10 +4945,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118636836</v>
+        <v>118639286</v>
       </c>
       <c r="B38" t="n">
-        <v>79601</v>
+        <v>79565</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5002,25 +4957,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5033,10 +4988,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>529422</v>
+        <v>529596</v>
       </c>
       <c r="R38" t="n">
-        <v>7168348</v>
+        <v>7168627</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -5084,26 +5039,6 @@
       <c r="AH38" t="inlineStr">
         <is>
           <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5121,10 +5056,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118640226</v>
+        <v>118639266</v>
       </c>
       <c r="B39" t="n">
-        <v>79594</v>
+        <v>78484</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5133,25 +5068,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5164,10 +5099,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>529825</v>
+        <v>529596</v>
       </c>
       <c r="R39" t="n">
-        <v>7168511</v>
+        <v>7168627</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -5214,27 +5149,7 @@
       </c>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>Högörtblandskog</t>
-        </is>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Blåbärsblandskog</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5252,10 +5167,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118638993</v>
+        <v>118636851</v>
       </c>
       <c r="B40" t="n">
-        <v>79594</v>
+        <v>78484</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5264,25 +5179,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5295,10 +5210,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>529785</v>
+        <v>529422</v>
       </c>
       <c r="R40" t="n">
-        <v>7168501</v>
+        <v>7168348</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5345,27 +5260,7 @@
       </c>
       <c r="AH40" t="inlineStr">
         <is>
-          <t>Högörtblandskog</t>
-        </is>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Blåbärsblandskog</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5383,10 +5278,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118639286</v>
+        <v>118640226</v>
       </c>
       <c r="B41" t="n">
-        <v>79565</v>
+        <v>79594</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5395,25 +5290,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5426,10 +5321,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>529596</v>
+        <v>529825</v>
       </c>
       <c r="R41" t="n">
-        <v>7168627</v>
+        <v>7168511</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5476,7 +5371,27 @@
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
+          <t>Högörtblandskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5494,10 +5409,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118637923</v>
+        <v>118640233</v>
       </c>
       <c r="B42" t="n">
-        <v>79601</v>
+        <v>79566</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5506,25 +5421,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5537,10 +5452,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>529679</v>
+        <v>529825</v>
       </c>
       <c r="R42" t="n">
-        <v>7168420</v>
+        <v>7168511</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5602,12 +5517,12 @@
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5625,10 +5540,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118640233</v>
+        <v>118640655</v>
       </c>
       <c r="B43" t="n">
-        <v>79566</v>
+        <v>104925</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5637,30 +5552,43 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2081</v>
+        <v>221725</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5668,10 +5596,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>529825</v>
+        <v>529831</v>
       </c>
       <c r="R43" t="n">
-        <v>7168511</v>
+        <v>7168496</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5719,26 +5647,6 @@
       <c r="AH43" t="inlineStr">
         <is>
           <t>Högörtblandskog</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5756,7 +5664,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118640655</v>
+        <v>118640485</v>
       </c>
       <c r="B44" t="n">
         <v>104925</v>
@@ -5812,10 +5720,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>529831</v>
+        <v>529812</v>
       </c>
       <c r="R44" t="n">
-        <v>7168496</v>
+        <v>7168477</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5880,7 +5788,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118638347</v>
+        <v>118636848</v>
       </c>
       <c r="B45" t="n">
         <v>79601</v>
@@ -5923,10 +5831,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>529581</v>
+        <v>529422</v>
       </c>
       <c r="R45" t="n">
-        <v>7168387</v>
+        <v>7168348</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5978,12 +5886,12 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AM45" t="inlineStr">
@@ -5993,7 +5901,7 @@
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6011,10 +5919,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118640485</v>
+        <v>118637579</v>
       </c>
       <c r="B46" t="n">
-        <v>104925</v>
+        <v>79601</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6027,39 +5935,26 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221725</v>
+        <v>6464</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr"/>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -6067,10 +5962,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>529812</v>
+        <v>529657</v>
       </c>
       <c r="R46" t="n">
-        <v>7168477</v>
+        <v>7168658</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -6118,6 +6013,26 @@
       <c r="AH46" t="inlineStr">
         <is>
           <t>Högörtblandskog</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6135,10 +6050,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118636851</v>
+        <v>118638226</v>
       </c>
       <c r="B47" t="n">
-        <v>78484</v>
+        <v>79601</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6147,25 +6062,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6178,10 +6093,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>529422</v>
+        <v>529407</v>
       </c>
       <c r="R47" t="n">
-        <v>7168348</v>
+        <v>7168450</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -6229,6 +6144,26 @@
       <c r="AH47" t="inlineStr">
         <is>
           <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6246,10 +6181,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118638521</v>
+        <v>118638030</v>
       </c>
       <c r="B48" t="n">
-        <v>78484</v>
+        <v>79601</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6258,25 +6193,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6289,10 +6224,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>529374</v>
+        <v>529474</v>
       </c>
       <c r="R48" t="n">
-        <v>7168443</v>
+        <v>7168472</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -6340,6 +6275,26 @@
       <c r="AH48" t="inlineStr">
         <is>
           <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6357,10 +6312,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118638226</v>
+        <v>118638993</v>
       </c>
       <c r="B49" t="n">
-        <v>79601</v>
+        <v>79594</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6373,21 +6328,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6400,10 +6355,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>529407</v>
+        <v>529785</v>
       </c>
       <c r="R49" t="n">
-        <v>7168450</v>
+        <v>7168501</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -6450,7 +6405,7 @@
       </c>
       <c r="AH49" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
+          <t>Högörtblandskog</t>
         </is>
       </c>
       <c r="AJ49" t="inlineStr">
@@ -6488,10 +6443,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118639270</v>
+        <v>118638559</v>
       </c>
       <c r="B50" t="n">
-        <v>79594</v>
+        <v>78484</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6500,25 +6455,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6531,10 +6486,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>529596</v>
+        <v>529439</v>
       </c>
       <c r="R50" t="n">
-        <v>7168627</v>
+        <v>7168447</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6582,6 +6537,26 @@
       <c r="AH50" t="inlineStr">
         <is>
           <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6599,10 +6574,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>118639266</v>
+        <v>118637923</v>
       </c>
       <c r="B51" t="n">
-        <v>78484</v>
+        <v>79601</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6611,25 +6586,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6642,10 +6617,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>529596</v>
+        <v>529679</v>
       </c>
       <c r="R51" t="n">
-        <v>7168627</v>
+        <v>7168420</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6692,7 +6667,27 @@
       </c>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
+          <t>Högörtblandskog</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6710,10 +6705,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>118638579</v>
+        <v>118637596</v>
       </c>
       <c r="B52" t="n">
-        <v>79601</v>
+        <v>78484</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6722,25 +6717,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6753,10 +6748,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>529439</v>
+        <v>529657</v>
       </c>
       <c r="R52" t="n">
-        <v>7168447</v>
+        <v>7168658</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6800,6 +6795,11 @@
       <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>Högörtblandskog</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">

--- a/artfynd/A 2227-2024 artfynd.xlsx
+++ b/artfynd/A 2227-2024 artfynd.xlsx
@@ -4617,10 +4617,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118639270</v>
+        <v>118638521</v>
       </c>
       <c r="B35" t="n">
-        <v>79594</v>
+        <v>78484</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4629,25 +4629,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4660,10 +4660,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>529596</v>
+        <v>529374</v>
       </c>
       <c r="R35" t="n">
-        <v>7168627</v>
+        <v>7168443</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4728,10 +4728,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118638521</v>
+        <v>118639270</v>
       </c>
       <c r="B36" t="n">
-        <v>78484</v>
+        <v>79594</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4740,25 +4740,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4771,10 +4771,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>529374</v>
+        <v>529596</v>
       </c>
       <c r="R36" t="n">
-        <v>7168443</v>
+        <v>7168627</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>

--- a/artfynd/A 2227-2024 artfynd.xlsx
+++ b/artfynd/A 2227-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118377115</v>
+        <v>118376570</v>
       </c>
       <c r="B2" t="n">
-        <v>98180</v>
+        <v>78484</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,43 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219880</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -731,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>529828</v>
+        <v>529817</v>
       </c>
       <c r="R2" t="n">
-        <v>7168693</v>
+        <v>7168518</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -799,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118377695</v>
+        <v>118376493</v>
       </c>
       <c r="B3" t="n">
-        <v>79601</v>
+        <v>78484</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -842,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>529416</v>
+        <v>529564</v>
       </c>
       <c r="R3" t="n">
-        <v>7168380</v>
+        <v>7168298</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -893,26 +880,6 @@
       <c r="AH3" t="inlineStr">
         <is>
           <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -930,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118377198</v>
+        <v>118374393</v>
       </c>
       <c r="B4" t="n">
-        <v>98180</v>
+        <v>97763</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -946,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219880</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -975,7 +942,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
@@ -986,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>529781</v>
+        <v>529828</v>
       </c>
       <c r="R4" t="n">
-        <v>7168708</v>
+        <v>7168707</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1022,6 +989,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-07-10</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>mer eller mindre fläckiga blad</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1054,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118373980</v>
+        <v>118374544</v>
       </c>
       <c r="B5" t="n">
-        <v>98180</v>
+        <v>97763</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1070,26 +1042,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219880</v>
+        <v>219790</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>37</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1099,7 +1071,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
@@ -1110,10 +1082,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>529729</v>
+        <v>529757</v>
       </c>
       <c r="R5" t="n">
-        <v>7168738</v>
+        <v>7168700</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1146,6 +1118,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-07-10</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>utan fläckar på bladen</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1178,10 +1155,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118376653</v>
+        <v>118373653</v>
       </c>
       <c r="B6" t="n">
-        <v>104925</v>
+        <v>97763</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1194,26 +1171,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221725</v>
+        <v>219790</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1234,10 +1211,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>529335</v>
+        <v>529821</v>
       </c>
       <c r="R6" t="n">
-        <v>7168411</v>
+        <v>7168618</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1272,6 +1249,11 @@
           <t>2024-07-10</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>stort område med tät förekomst. Många med blad utan fläckar.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1281,11 +1263,6 @@
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1302,10 +1279,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118376507</v>
+        <v>118377821</v>
       </c>
       <c r="B7" t="n">
-        <v>78484</v>
+        <v>79601</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1314,25 +1291,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1345,10 +1322,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>529596</v>
+        <v>529473</v>
       </c>
       <c r="R7" t="n">
-        <v>7168313</v>
+        <v>7168495</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1396,6 +1373,26 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1413,10 +1410,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118372729</v>
+        <v>118376346</v>
       </c>
       <c r="B8" t="n">
-        <v>97763</v>
+        <v>78484</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1425,43 +1422,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1469,10 +1453,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>529835</v>
+        <v>529375</v>
       </c>
       <c r="R8" t="n">
-        <v>7168557</v>
+        <v>7168391</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1519,7 +1503,7 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Blandsumpskog</t>
+          <t>Blåbärsblandskog</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1537,10 +1521,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118372553</v>
+        <v>118376431</v>
       </c>
       <c r="B9" t="n">
-        <v>97763</v>
+        <v>78484</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1549,43 +1533,30 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1593,10 +1564,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>529778</v>
+        <v>529430</v>
       </c>
       <c r="R9" t="n">
-        <v>7168467</v>
+        <v>7168343</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1643,7 +1614,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Blandsumpskog</t>
+          <t>Blåbärsblandskog</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1661,10 +1632,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118374393</v>
+        <v>118374825</v>
       </c>
       <c r="B10" t="n">
-        <v>97763</v>
+        <v>78484</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1673,43 +1644,30 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1717,10 +1675,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>529828</v>
+        <v>529615</v>
       </c>
       <c r="R10" t="n">
-        <v>7168707</v>
+        <v>7168654</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1755,11 +1713,6 @@
           <t>2024-07-10</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>mer eller mindre fläckiga blad</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1772,7 +1725,7 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Blandsumpskog</t>
+          <t>Högörtblandskog</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1790,10 +1743,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118377497</v>
+        <v>118376619</v>
       </c>
       <c r="B11" t="n">
-        <v>79601</v>
+        <v>78484</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1802,25 +1755,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1833,10 +1786,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>529366</v>
+        <v>529335</v>
       </c>
       <c r="R11" t="n">
-        <v>7168437</v>
+        <v>7168411</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1884,26 +1837,6 @@
       <c r="AH11" t="inlineStr">
         <is>
           <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1921,10 +1854,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118377613</v>
+        <v>118376886</v>
       </c>
       <c r="B12" t="n">
-        <v>79601</v>
+        <v>98180</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1937,26 +1870,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6464</v>
+        <v>219880</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1964,10 +1910,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>529724</v>
+        <v>529825</v>
       </c>
       <c r="R12" t="n">
-        <v>7168444</v>
+        <v>7168680</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -2014,27 +1960,7 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Blandsumpskog</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2052,10 +1978,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118376364</v>
+        <v>118373980</v>
       </c>
       <c r="B13" t="n">
-        <v>78484</v>
+        <v>98180</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2064,30 +1990,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>219880</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2095,10 +2034,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>529409</v>
+        <v>529729</v>
       </c>
       <c r="R13" t="n">
-        <v>7168367</v>
+        <v>7168738</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2145,7 +2084,7 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
+          <t>Blandsumpskog</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2163,7 +2102,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118374825</v>
+        <v>118376553</v>
       </c>
       <c r="B14" t="n">
         <v>78484</v>
@@ -2206,10 +2145,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>529615</v>
+        <v>529742</v>
       </c>
       <c r="R14" t="n">
-        <v>7168654</v>
+        <v>7168447</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2256,7 +2195,7 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Högörtblandskog</t>
+          <t>Blandsumpskog</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2274,7 +2213,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118376493</v>
+        <v>118376364</v>
       </c>
       <c r="B15" t="n">
         <v>78484</v>
@@ -2317,10 +2256,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>529564</v>
+        <v>529409</v>
       </c>
       <c r="R15" t="n">
-        <v>7168298</v>
+        <v>7168367</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2385,10 +2324,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118376346</v>
+        <v>118377695</v>
       </c>
       <c r="B16" t="n">
-        <v>78484</v>
+        <v>79601</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2397,25 +2336,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2428,10 +2367,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>529375</v>
+        <v>529416</v>
       </c>
       <c r="R16" t="n">
-        <v>7168391</v>
+        <v>7168380</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2479,6 +2418,26 @@
       <c r="AH16" t="inlineStr">
         <is>
           <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2496,10 +2455,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118376316</v>
+        <v>118372553</v>
       </c>
       <c r="B17" t="n">
-        <v>78484</v>
+        <v>97763</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2508,30 +2467,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2539,10 +2511,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>529455</v>
+        <v>529778</v>
       </c>
       <c r="R17" t="n">
-        <v>7168453</v>
+        <v>7168467</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2589,7 +2561,7 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
+          <t>Blandsumpskog</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2607,10 +2579,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118374236</v>
+        <v>118376653</v>
       </c>
       <c r="B18" t="n">
-        <v>97867</v>
+        <v>104925</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2623,26 +2595,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221952</v>
+        <v>221725</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2663,10 +2635,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>529691</v>
+        <v>529335</v>
       </c>
       <c r="R18" t="n">
-        <v>7168682</v>
+        <v>7168411</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2713,7 +2685,7 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Blandsumpskog</t>
+          <t>Blåbärsblandskog</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2731,10 +2703,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118374116</v>
+        <v>118377497</v>
       </c>
       <c r="B19" t="n">
-        <v>97763</v>
+        <v>79601</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2747,39 +2719,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219790</v>
+        <v>6464</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2787,10 +2746,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>529691</v>
+        <v>529366</v>
       </c>
       <c r="R19" t="n">
-        <v>7168682</v>
+        <v>7168437</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2837,7 +2796,27 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>Blandsumpskog</t>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2855,10 +2834,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118373894</v>
+        <v>118376316</v>
       </c>
       <c r="B20" t="n">
-        <v>97763</v>
+        <v>78484</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2867,43 +2846,30 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2911,10 +2877,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>529729</v>
+        <v>529455</v>
       </c>
       <c r="R20" t="n">
-        <v>7168738</v>
+        <v>7168453</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2961,7 +2927,7 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Blandsumpskog</t>
+          <t>Blåbärsblandskog</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2979,10 +2945,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118374699</v>
+        <v>118372729</v>
       </c>
       <c r="B21" t="n">
-        <v>78484</v>
+        <v>97763</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2991,30 +2957,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3022,10 +3001,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>529749</v>
+        <v>529835</v>
       </c>
       <c r="R21" t="n">
-        <v>7168733</v>
+        <v>7168557</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -3090,7 +3069,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118373990</v>
+        <v>118376237</v>
       </c>
       <c r="B22" t="n">
         <v>78484</v>
@@ -3133,10 +3112,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>529729</v>
+        <v>529559</v>
       </c>
       <c r="R22" t="n">
-        <v>7168738</v>
+        <v>7168596</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3183,7 +3162,7 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>Blandsumpskog</t>
+          <t>Blåbärsblandskog</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3201,7 +3180,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118376553</v>
+        <v>118373990</v>
       </c>
       <c r="B23" t="n">
         <v>78484</v>
@@ -3244,10 +3223,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>529742</v>
+        <v>529729</v>
       </c>
       <c r="R23" t="n">
-        <v>7168447</v>
+        <v>7168738</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3312,10 +3291,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118374787</v>
+        <v>118377613</v>
       </c>
       <c r="B24" t="n">
-        <v>78484</v>
+        <v>79601</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3324,25 +3303,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3355,10 +3334,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>529672</v>
+        <v>529724</v>
       </c>
       <c r="R24" t="n">
-        <v>7168655</v>
+        <v>7168444</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3405,7 +3384,27 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Högörtblandskog</t>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3423,10 +3422,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118376570</v>
+        <v>118374236</v>
       </c>
       <c r="B25" t="n">
-        <v>78484</v>
+        <v>97867</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3435,30 +3434,43 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3466,10 +3478,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>529817</v>
+        <v>529691</v>
       </c>
       <c r="R25" t="n">
-        <v>7168518</v>
+        <v>7168682</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3534,10 +3546,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118374544</v>
+        <v>118374787</v>
       </c>
       <c r="B26" t="n">
-        <v>97763</v>
+        <v>78484</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3546,43 +3558,30 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3590,10 +3589,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>529757</v>
+        <v>529672</v>
       </c>
       <c r="R26" t="n">
-        <v>7168700</v>
+        <v>7168655</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3628,11 +3627,6 @@
           <t>2024-07-10</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>utan fläckar på bladen</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3645,7 +3639,7 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Blandsumpskog</t>
+          <t>Högörtblandskog</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3663,10 +3657,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118376886</v>
+        <v>118373894</v>
       </c>
       <c r="B27" t="n">
-        <v>98180</v>
+        <v>97763</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3679,26 +3673,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219880</v>
+        <v>219790</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3708,7 +3702,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
@@ -3719,10 +3713,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>529825</v>
+        <v>529729</v>
       </c>
       <c r="R27" t="n">
-        <v>7168680</v>
+        <v>7168738</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3787,10 +3781,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118373653</v>
+        <v>118377198</v>
       </c>
       <c r="B28" t="n">
-        <v>97763</v>
+        <v>98180</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3803,26 +3797,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219790</v>
+        <v>219880</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3832,7 +3826,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L28" t="inlineStr"/>
@@ -3843,10 +3837,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>529821</v>
+        <v>529781</v>
       </c>
       <c r="R28" t="n">
-        <v>7168618</v>
+        <v>7168708</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3881,11 +3875,6 @@
           <t>2024-07-10</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>stort område med tät förekomst. Många med blad utan fläckar.</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3895,6 +3884,11 @@
       <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Blandsumpskog</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3911,10 +3905,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118377821</v>
+        <v>118376507</v>
       </c>
       <c r="B29" t="n">
-        <v>79601</v>
+        <v>78484</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3923,25 +3917,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3954,10 +3948,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>529473</v>
+        <v>529596</v>
       </c>
       <c r="R29" t="n">
-        <v>7168495</v>
+        <v>7168313</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -4005,26 +3999,6 @@
       <c r="AH29" t="inlineStr">
         <is>
           <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4042,10 +4016,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118376431</v>
+        <v>118377115</v>
       </c>
       <c r="B30" t="n">
-        <v>78484</v>
+        <v>98180</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4054,30 +4028,43 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>219880</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4085,10 +4072,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>529430</v>
+        <v>529828</v>
       </c>
       <c r="R30" t="n">
-        <v>7168343</v>
+        <v>7168693</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -4135,7 +4122,7 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
+          <t>Blandsumpskog</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4153,7 +4140,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118376521</v>
+        <v>118374699</v>
       </c>
       <c r="B31" t="n">
         <v>78484</v>
@@ -4196,10 +4183,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>529657</v>
+        <v>529749</v>
       </c>
       <c r="R31" t="n">
-        <v>7168427</v>
+        <v>7168733</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4246,7 +4233,7 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
+          <t>Blandsumpskog</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4264,7 +4251,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118376237</v>
+        <v>118376521</v>
       </c>
       <c r="B32" t="n">
         <v>78484</v>
@@ -4307,10 +4294,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>529559</v>
+        <v>529657</v>
       </c>
       <c r="R32" t="n">
-        <v>7168596</v>
+        <v>7168427</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4375,10 +4362,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118376619</v>
+        <v>118374116</v>
       </c>
       <c r="B33" t="n">
-        <v>78484</v>
+        <v>97763</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4387,30 +4374,43 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4418,10 +4418,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>529335</v>
+        <v>529691</v>
       </c>
       <c r="R33" t="n">
-        <v>7168411</v>
+        <v>7168682</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
+          <t>Blandsumpskog</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4486,10 +4486,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118638347</v>
+        <v>118637596</v>
       </c>
       <c r="B34" t="n">
-        <v>79601</v>
+        <v>78484</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4498,25 +4498,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4529,10 +4529,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>529581</v>
+        <v>529657</v>
       </c>
       <c r="R34" t="n">
-        <v>7168387</v>
+        <v>7168658</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4579,27 +4579,7 @@
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Högörtblandskog</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4617,10 +4597,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118638521</v>
+        <v>118638226</v>
       </c>
       <c r="B35" t="n">
-        <v>78484</v>
+        <v>79601</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4629,25 +4609,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4660,10 +4640,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>529374</v>
+        <v>529407</v>
       </c>
       <c r="R35" t="n">
-        <v>7168443</v>
+        <v>7168450</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4711,6 +4691,26 @@
       <c r="AH35" t="inlineStr">
         <is>
           <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4728,10 +4728,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118639270</v>
+        <v>118640655</v>
       </c>
       <c r="B36" t="n">
-        <v>79594</v>
+        <v>104925</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4744,26 +4744,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6462</v>
+        <v>221725</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4771,10 +4784,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>529596</v>
+        <v>529831</v>
       </c>
       <c r="R36" t="n">
-        <v>7168627</v>
+        <v>7168496</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4821,7 +4834,7 @@
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
+          <t>Högörtblandskog</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4839,10 +4852,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118638579</v>
+        <v>118640485</v>
       </c>
       <c r="B37" t="n">
-        <v>79601</v>
+        <v>104925</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4855,26 +4868,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6464</v>
+        <v>221725</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4882,10 +4908,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>529439</v>
+        <v>529812</v>
       </c>
       <c r="R37" t="n">
-        <v>7168447</v>
+        <v>7168477</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4929,6 +4955,11 @@
       <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Högörtblandskog</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4945,10 +4976,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118639286</v>
+        <v>118636851</v>
       </c>
       <c r="B38" t="n">
-        <v>79565</v>
+        <v>78484</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4961,21 +4992,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4988,10 +5019,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>529596</v>
+        <v>529422</v>
       </c>
       <c r="R38" t="n">
-        <v>7168627</v>
+        <v>7168348</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -5056,10 +5087,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118639266</v>
+        <v>118638993</v>
       </c>
       <c r="B39" t="n">
-        <v>78484</v>
+        <v>79594</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5068,25 +5099,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5099,10 +5130,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>529596</v>
+        <v>529785</v>
       </c>
       <c r="R39" t="n">
-        <v>7168627</v>
+        <v>7168501</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -5149,7 +5180,27 @@
       </c>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
+          <t>Högörtblandskog</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5167,10 +5218,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118636851</v>
+        <v>118640226</v>
       </c>
       <c r="B40" t="n">
-        <v>78484</v>
+        <v>79594</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5179,25 +5230,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5210,10 +5261,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>529422</v>
+        <v>529825</v>
       </c>
       <c r="R40" t="n">
-        <v>7168348</v>
+        <v>7168511</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5260,7 +5311,27 @@
       </c>
       <c r="AH40" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
+          <t>Högörtblandskog</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5278,10 +5349,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118640226</v>
+        <v>118636848</v>
       </c>
       <c r="B41" t="n">
-        <v>79594</v>
+        <v>79601</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5294,21 +5365,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5321,10 +5392,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>529825</v>
+        <v>529422</v>
       </c>
       <c r="R41" t="n">
-        <v>7168511</v>
+        <v>7168348</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5371,27 +5442,27 @@
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>Högörtblandskog</t>
+          <t>Blåbärsblandskog</t>
         </is>
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5409,10 +5480,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118640233</v>
+        <v>118639270</v>
       </c>
       <c r="B42" t="n">
-        <v>79566</v>
+        <v>79594</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5421,25 +5492,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5452,10 +5523,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>529825</v>
+        <v>529596</v>
       </c>
       <c r="R42" t="n">
-        <v>7168511</v>
+        <v>7168627</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5502,27 +5573,7 @@
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>Högörtblandskog</t>
-        </is>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Blåbärsblandskog</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5540,10 +5591,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118640655</v>
+        <v>118639266</v>
       </c>
       <c r="B43" t="n">
-        <v>104925</v>
+        <v>78484</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5552,43 +5603,30 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221725</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5596,10 +5634,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>529831</v>
+        <v>529596</v>
       </c>
       <c r="R43" t="n">
-        <v>7168496</v>
+        <v>7168627</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5646,7 +5684,7 @@
       </c>
       <c r="AH43" t="inlineStr">
         <is>
-          <t>Högörtblandskog</t>
+          <t>Blåbärsblandskog</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5664,10 +5702,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118640485</v>
+        <v>118637579</v>
       </c>
       <c r="B44" t="n">
-        <v>104925</v>
+        <v>79601</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5680,39 +5718,26 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221725</v>
+        <v>6464</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr"/>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5720,10 +5745,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>529812</v>
+        <v>529657</v>
       </c>
       <c r="R44" t="n">
-        <v>7168477</v>
+        <v>7168658</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5771,6 +5796,26 @@
       <c r="AH44" t="inlineStr">
         <is>
           <t>Högörtblandskog</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5788,7 +5833,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118636848</v>
+        <v>118638509</v>
       </c>
       <c r="B45" t="n">
         <v>79601</v>
@@ -5831,10 +5876,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>529422</v>
+        <v>529374</v>
       </c>
       <c r="R45" t="n">
-        <v>7168348</v>
+        <v>7168443</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5886,12 +5931,12 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM45" t="inlineStr">
@@ -5901,7 +5946,7 @@
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -5919,7 +5964,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118637579</v>
+        <v>118637923</v>
       </c>
       <c r="B46" t="n">
         <v>79601</v>
@@ -5962,10 +6007,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>529657</v>
+        <v>529679</v>
       </c>
       <c r="R46" t="n">
-        <v>7168658</v>
+        <v>7168420</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -6027,12 +6072,12 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6050,7 +6095,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118638226</v>
+        <v>118638347</v>
       </c>
       <c r="B47" t="n">
         <v>79601</v>
@@ -6093,10 +6138,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>529407</v>
+        <v>529581</v>
       </c>
       <c r="R47" t="n">
-        <v>7168450</v>
+        <v>7168387</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -6181,10 +6226,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118638030</v>
+        <v>118639286</v>
       </c>
       <c r="B48" t="n">
-        <v>79601</v>
+        <v>79565</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6193,25 +6238,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6224,10 +6269,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>529474</v>
+        <v>529596</v>
       </c>
       <c r="R48" t="n">
-        <v>7168472</v>
+        <v>7168627</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -6275,26 +6320,6 @@
       <c r="AH48" t="inlineStr">
         <is>
           <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6312,10 +6337,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118638993</v>
+        <v>118638579</v>
       </c>
       <c r="B49" t="n">
-        <v>79594</v>
+        <v>79601</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6328,21 +6353,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6355,10 +6380,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>529785</v>
+        <v>529439</v>
       </c>
       <c r="R49" t="n">
-        <v>7168501</v>
+        <v>7168447</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -6402,31 +6427,6 @@
       <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>Högörtblandskog</t>
-        </is>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6443,10 +6443,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118638559</v>
+        <v>118638030</v>
       </c>
       <c r="B50" t="n">
-        <v>78484</v>
+        <v>79601</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6455,25 +6455,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6486,10 +6486,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>529439</v>
+        <v>529474</v>
       </c>
       <c r="R50" t="n">
-        <v>7168447</v>
+        <v>7168472</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6574,10 +6574,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>118637923</v>
+        <v>118638559</v>
       </c>
       <c r="B51" t="n">
-        <v>79601</v>
+        <v>78484</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6586,25 +6586,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6617,10 +6617,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>529679</v>
+        <v>529439</v>
       </c>
       <c r="R51" t="n">
-        <v>7168420</v>
+        <v>7168447</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6667,7 +6667,7 @@
       </c>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>Högörtblandskog</t>
+          <t>Blåbärsblandskog</t>
         </is>
       </c>
       <c r="AJ51" t="inlineStr">
@@ -6705,7 +6705,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>118637596</v>
+        <v>118638521</v>
       </c>
       <c r="B52" t="n">
         <v>78484</v>
@@ -6748,10 +6748,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>529657</v>
+        <v>529374</v>
       </c>
       <c r="R52" t="n">
-        <v>7168658</v>
+        <v>7168443</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6798,7 +6798,7 @@
       </c>
       <c r="AH52" t="inlineStr">
         <is>
-          <t>Högörtblandskog</t>
+          <t>Blåbärsblandskog</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6816,10 +6816,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>118638509</v>
+        <v>118640233</v>
       </c>
       <c r="B53" t="n">
-        <v>79601</v>
+        <v>79566</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6828,25 +6828,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6859,10 +6859,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>529374</v>
+        <v>529825</v>
       </c>
       <c r="R53" t="n">
-        <v>7168443</v>
+        <v>7168511</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6909,7 +6909,7 @@
       </c>
       <c r="AH53" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
+          <t>Högörtblandskog</t>
         </is>
       </c>
       <c r="AJ53" t="inlineStr">
@@ -6924,12 +6924,12 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>

--- a/artfynd/A 2227-2024 artfynd.xlsx
+++ b/artfynd/A 2227-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118376570</v>
+        <v>118377695</v>
       </c>
       <c r="B2" t="n">
-        <v>78484</v>
+        <v>79608</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>529817</v>
+        <v>529416</v>
       </c>
       <c r="R2" t="n">
-        <v>7168518</v>
+        <v>7168380</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -768,7 +768,27 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Blandsumpskog</t>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -786,10 +806,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118376493</v>
+        <v>118373894</v>
       </c>
       <c r="B3" t="n">
-        <v>78484</v>
+        <v>97770</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,30 +818,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -829,10 +862,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>529564</v>
+        <v>529729</v>
       </c>
       <c r="R3" t="n">
-        <v>7168298</v>
+        <v>7168738</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -879,7 +912,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
+          <t>Blandsumpskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -897,10 +930,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118374393</v>
+        <v>118377198</v>
       </c>
       <c r="B4" t="n">
-        <v>97763</v>
+        <v>98187</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +946,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>219880</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -942,7 +975,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
@@ -953,10 +986,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>529828</v>
+        <v>529781</v>
       </c>
       <c r="R4" t="n">
-        <v>7168707</v>
+        <v>7168708</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -989,11 +1022,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-07-10</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>mer eller mindre fläckiga blad</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,10 +1054,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118374544</v>
+        <v>118374825</v>
       </c>
       <c r="B5" t="n">
-        <v>97763</v>
+        <v>78491</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1038,43 +1066,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1082,10 +1097,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>529757</v>
+        <v>529615</v>
       </c>
       <c r="R5" t="n">
-        <v>7168700</v>
+        <v>7168654</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1120,11 +1135,6 @@
           <t>2024-07-10</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>utan fläckar på bladen</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1137,7 +1147,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Blandsumpskog</t>
+          <t>Högörtblandskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1155,10 +1165,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118373653</v>
+        <v>118376316</v>
       </c>
       <c r="B6" t="n">
-        <v>97763</v>
+        <v>78491</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1167,43 +1177,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1211,10 +1208,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>529821</v>
+        <v>529455</v>
       </c>
       <c r="R6" t="n">
-        <v>7168618</v>
+        <v>7168453</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1249,11 +1246,6 @@
           <t>2024-07-10</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>stort område med tät förekomst. Många med blad utan fläckar.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1263,6 +1255,11 @@
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1279,10 +1276,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118377821</v>
+        <v>118374787</v>
       </c>
       <c r="B7" t="n">
-        <v>79601</v>
+        <v>78491</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1291,25 +1288,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1322,10 +1319,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>529473</v>
+        <v>529672</v>
       </c>
       <c r="R7" t="n">
-        <v>7168495</v>
+        <v>7168655</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1372,27 +1369,7 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Högörtblandskog</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1410,10 +1387,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118376346</v>
+        <v>118377613</v>
       </c>
       <c r="B8" t="n">
-        <v>78484</v>
+        <v>79608</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1422,25 +1399,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1453,10 +1430,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>529375</v>
+        <v>529724</v>
       </c>
       <c r="R8" t="n">
-        <v>7168391</v>
+        <v>7168444</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1504,6 +1481,26 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1521,10 +1518,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118376431</v>
+        <v>118377115</v>
       </c>
       <c r="B9" t="n">
-        <v>78484</v>
+        <v>98187</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1533,30 +1530,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>219880</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1564,10 +1574,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>529430</v>
+        <v>529828</v>
       </c>
       <c r="R9" t="n">
-        <v>7168343</v>
+        <v>7168693</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1614,7 +1624,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
+          <t>Blandsumpskog</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1632,10 +1642,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118374825</v>
+        <v>118374393</v>
       </c>
       <c r="B10" t="n">
-        <v>78484</v>
+        <v>97770</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1644,30 +1654,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1675,10 +1698,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>529615</v>
+        <v>529828</v>
       </c>
       <c r="R10" t="n">
-        <v>7168654</v>
+        <v>7168707</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1713,6 +1736,11 @@
           <t>2024-07-10</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>mer eller mindre fläckiga blad</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1725,7 +1753,7 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Högörtblandskog</t>
+          <t>Blandsumpskog</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1743,10 +1771,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118376619</v>
+        <v>118372553</v>
       </c>
       <c r="B11" t="n">
-        <v>78484</v>
+        <v>97770</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1755,30 +1783,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1786,10 +1827,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>529335</v>
+        <v>529778</v>
       </c>
       <c r="R11" t="n">
-        <v>7168411</v>
+        <v>7168467</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1836,7 +1877,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
+          <t>Blandsumpskog</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1854,10 +1895,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118376886</v>
+        <v>118374544</v>
       </c>
       <c r="B12" t="n">
-        <v>98180</v>
+        <v>97770</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1870,26 +1911,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219880</v>
+        <v>219790</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>37</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1899,7 +1940,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
@@ -1910,10 +1951,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>529825</v>
+        <v>529757</v>
       </c>
       <c r="R12" t="n">
-        <v>7168680</v>
+        <v>7168700</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1946,6 +1987,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-07-10</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>utan fläckar på bladen</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1978,10 +2024,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118373980</v>
+        <v>118374236</v>
       </c>
       <c r="B13" t="n">
-        <v>98180</v>
+        <v>97874</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1994,26 +2040,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219880</v>
+        <v>221952</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2023,7 +2069,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
@@ -2034,10 +2080,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>529729</v>
+        <v>529691</v>
       </c>
       <c r="R13" t="n">
-        <v>7168738</v>
+        <v>7168682</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2102,10 +2148,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118376553</v>
+        <v>118376364</v>
       </c>
       <c r="B14" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2145,10 +2191,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>529742</v>
+        <v>529409</v>
       </c>
       <c r="R14" t="n">
-        <v>7168447</v>
+        <v>7168367</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2195,7 +2241,7 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Blandsumpskog</t>
+          <t>Blåbärsblandskog</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2213,10 +2259,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118376364</v>
+        <v>118376493</v>
       </c>
       <c r="B15" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2256,10 +2302,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>529409</v>
+        <v>529564</v>
       </c>
       <c r="R15" t="n">
-        <v>7168367</v>
+        <v>7168298</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2324,10 +2370,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118377695</v>
+        <v>118373990</v>
       </c>
       <c r="B16" t="n">
-        <v>79601</v>
+        <v>78491</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2336,25 +2382,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2367,10 +2413,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>529416</v>
+        <v>529729</v>
       </c>
       <c r="R16" t="n">
-        <v>7168380</v>
+        <v>7168738</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2417,27 +2463,7 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Blandsumpskog</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2455,10 +2481,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118372553</v>
+        <v>118376553</v>
       </c>
       <c r="B17" t="n">
-        <v>97763</v>
+        <v>78491</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2467,43 +2493,30 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2511,10 +2524,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>529778</v>
+        <v>529742</v>
       </c>
       <c r="R17" t="n">
-        <v>7168467</v>
+        <v>7168447</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2579,10 +2592,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118376653</v>
+        <v>118376237</v>
       </c>
       <c r="B18" t="n">
-        <v>104925</v>
+        <v>78491</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2591,43 +2604,30 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221725</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2635,10 +2635,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>529335</v>
+        <v>529559</v>
       </c>
       <c r="R18" t="n">
-        <v>7168411</v>
+        <v>7168596</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2703,10 +2703,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118377497</v>
+        <v>118376521</v>
       </c>
       <c r="B19" t="n">
-        <v>79601</v>
+        <v>78491</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2715,25 +2715,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2746,10 +2746,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>529366</v>
+        <v>529657</v>
       </c>
       <c r="R19" t="n">
-        <v>7168437</v>
+        <v>7168427</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2797,26 +2797,6 @@
       <c r="AH19" t="inlineStr">
         <is>
           <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2834,10 +2814,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118376316</v>
+        <v>118376346</v>
       </c>
       <c r="B20" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2877,10 +2857,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>529455</v>
+        <v>529375</v>
       </c>
       <c r="R20" t="n">
-        <v>7168453</v>
+        <v>7168391</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2945,10 +2925,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118372729</v>
+        <v>118373653</v>
       </c>
       <c r="B21" t="n">
-        <v>97763</v>
+        <v>97770</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2980,7 +2960,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3001,10 +2981,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>529835</v>
+        <v>529821</v>
       </c>
       <c r="R21" t="n">
-        <v>7168557</v>
+        <v>7168618</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -3039,6 +3019,11 @@
           <t>2024-07-10</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>stort område med tät förekomst. Många med blad utan fläckar.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3048,11 +3033,6 @@
       <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Blandsumpskog</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3069,10 +3049,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118376237</v>
+        <v>118374116</v>
       </c>
       <c r="B22" t="n">
-        <v>78484</v>
+        <v>97770</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3081,30 +3061,43 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3112,10 +3105,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>529559</v>
+        <v>529691</v>
       </c>
       <c r="R22" t="n">
-        <v>7168596</v>
+        <v>7168682</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3162,7 +3155,7 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
+          <t>Blandsumpskog</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3180,10 +3173,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118373990</v>
+        <v>118376507</v>
       </c>
       <c r="B23" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3223,10 +3216,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>529729</v>
+        <v>529596</v>
       </c>
       <c r="R23" t="n">
-        <v>7168738</v>
+        <v>7168313</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3273,7 +3266,7 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Blandsumpskog</t>
+          <t>Blåbärsblandskog</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3291,10 +3284,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118377613</v>
+        <v>118376619</v>
       </c>
       <c r="B24" t="n">
-        <v>79601</v>
+        <v>78491</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3303,25 +3296,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3334,10 +3327,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>529724</v>
+        <v>529335</v>
       </c>
       <c r="R24" t="n">
-        <v>7168444</v>
+        <v>7168411</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3385,26 +3378,6 @@
       <c r="AH24" t="inlineStr">
         <is>
           <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3422,10 +3395,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118374236</v>
+        <v>118376653</v>
       </c>
       <c r="B25" t="n">
-        <v>97867</v>
+        <v>104932</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3438,26 +3411,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221952</v>
+        <v>221725</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3478,10 +3451,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>529691</v>
+        <v>529335</v>
       </c>
       <c r="R25" t="n">
-        <v>7168682</v>
+        <v>7168411</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3528,7 +3501,7 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>Blandsumpskog</t>
+          <t>Blåbärsblandskog</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3546,10 +3519,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118374787</v>
+        <v>118377821</v>
       </c>
       <c r="B26" t="n">
-        <v>78484</v>
+        <v>79608</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3558,25 +3531,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3589,10 +3562,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>529672</v>
+        <v>529473</v>
       </c>
       <c r="R26" t="n">
-        <v>7168655</v>
+        <v>7168495</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3639,7 +3612,27 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Högörtblandskog</t>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3657,10 +3650,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118373894</v>
+        <v>118376570</v>
       </c>
       <c r="B27" t="n">
-        <v>97763</v>
+        <v>78491</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3669,43 +3662,30 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3713,10 +3693,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>529729</v>
+        <v>529817</v>
       </c>
       <c r="R27" t="n">
-        <v>7168738</v>
+        <v>7168518</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3781,10 +3761,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118377198</v>
+        <v>118373980</v>
       </c>
       <c r="B28" t="n">
-        <v>98180</v>
+        <v>98187</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3816,7 +3796,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3826,7 +3806,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L28" t="inlineStr"/>
@@ -3837,10 +3817,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>529781</v>
+        <v>529729</v>
       </c>
       <c r="R28" t="n">
-        <v>7168708</v>
+        <v>7168738</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3905,10 +3885,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118376507</v>
+        <v>118374699</v>
       </c>
       <c r="B29" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3948,10 +3928,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>529596</v>
+        <v>529749</v>
       </c>
       <c r="R29" t="n">
-        <v>7168313</v>
+        <v>7168733</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3998,7 +3978,7 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
+          <t>Blandsumpskog</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4016,10 +3996,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118377115</v>
+        <v>118376431</v>
       </c>
       <c r="B30" t="n">
-        <v>98180</v>
+        <v>78491</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4028,43 +4008,30 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219880</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4072,10 +4039,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>529828</v>
+        <v>529430</v>
       </c>
       <c r="R30" t="n">
-        <v>7168693</v>
+        <v>7168343</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -4122,7 +4089,7 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Blandsumpskog</t>
+          <t>Blåbärsblandskog</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4140,10 +4107,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118374699</v>
+        <v>118376886</v>
       </c>
       <c r="B31" t="n">
-        <v>78484</v>
+        <v>98187</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4152,30 +4119,43 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>219880</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4183,10 +4163,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>529749</v>
+        <v>529825</v>
       </c>
       <c r="R31" t="n">
-        <v>7168733</v>
+        <v>7168680</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4251,10 +4231,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118376521</v>
+        <v>118372729</v>
       </c>
       <c r="B32" t="n">
-        <v>78484</v>
+        <v>97770</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4263,30 +4243,43 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4294,10 +4287,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>529657</v>
+        <v>529835</v>
       </c>
       <c r="R32" t="n">
-        <v>7168427</v>
+        <v>7168557</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4344,7 +4337,7 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
+          <t>Blandsumpskog</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4362,10 +4355,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118374116</v>
+        <v>118377497</v>
       </c>
       <c r="B33" t="n">
-        <v>97763</v>
+        <v>79608</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4378,39 +4371,26 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>219790</v>
+        <v>6464</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr"/>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4418,10 +4398,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>529691</v>
+        <v>529366</v>
       </c>
       <c r="R33" t="n">
-        <v>7168682</v>
+        <v>7168437</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4468,7 +4448,27 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>Blandsumpskog</t>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4486,10 +4486,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118637596</v>
+        <v>118638521</v>
       </c>
       <c r="B34" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4529,10 +4529,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>529657</v>
+        <v>529374</v>
       </c>
       <c r="R34" t="n">
-        <v>7168658</v>
+        <v>7168443</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4579,7 +4579,7 @@
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>Högörtblandskog</t>
+          <t>Blåbärsblandskog</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4597,10 +4597,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118638226</v>
+        <v>118639266</v>
       </c>
       <c r="B35" t="n">
-        <v>79601</v>
+        <v>78491</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4609,25 +4609,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4640,10 +4640,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>529407</v>
+        <v>529596</v>
       </c>
       <c r="R35" t="n">
-        <v>7168450</v>
+        <v>7168627</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4691,26 +4691,6 @@
       <c r="AH35" t="inlineStr">
         <is>
           <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4728,10 +4708,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118640655</v>
+        <v>118638993</v>
       </c>
       <c r="B36" t="n">
-        <v>104925</v>
+        <v>79601</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4744,39 +4724,26 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221725</v>
+        <v>6462</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr"/>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4784,10 +4751,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>529831</v>
+        <v>529785</v>
       </c>
       <c r="R36" t="n">
-        <v>7168496</v>
+        <v>7168501</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4835,6 +4802,26 @@
       <c r="AH36" t="inlineStr">
         <is>
           <t>Högörtblandskog</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4852,10 +4839,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118640485</v>
+        <v>118639270</v>
       </c>
       <c r="B37" t="n">
-        <v>104925</v>
+        <v>79601</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4868,39 +4855,26 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221725</v>
+        <v>6462</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr"/>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4908,10 +4882,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>529812</v>
+        <v>529596</v>
       </c>
       <c r="R37" t="n">
-        <v>7168477</v>
+        <v>7168627</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4958,7 +4932,7 @@
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>Högörtblandskog</t>
+          <t>Blåbärsblandskog</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4976,10 +4950,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118636851</v>
+        <v>118639286</v>
       </c>
       <c r="B38" t="n">
-        <v>78484</v>
+        <v>79572</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4992,21 +4966,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5019,10 +4993,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>529422</v>
+        <v>529596</v>
       </c>
       <c r="R38" t="n">
-        <v>7168348</v>
+        <v>7168627</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -5087,10 +5061,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118638993</v>
+        <v>118638347</v>
       </c>
       <c r="B39" t="n">
-        <v>79594</v>
+        <v>79608</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5103,21 +5077,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5130,10 +5104,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>529785</v>
+        <v>529581</v>
       </c>
       <c r="R39" t="n">
-        <v>7168501</v>
+        <v>7168387</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -5180,7 +5154,7 @@
       </c>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>Högörtblandskog</t>
+          <t>Blåbärsblandskog</t>
         </is>
       </c>
       <c r="AJ39" t="inlineStr">
@@ -5218,10 +5192,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118640226</v>
+        <v>118636848</v>
       </c>
       <c r="B40" t="n">
-        <v>79594</v>
+        <v>79608</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5234,21 +5208,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5261,10 +5235,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>529825</v>
+        <v>529422</v>
       </c>
       <c r="R40" t="n">
-        <v>7168511</v>
+        <v>7168348</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5311,27 +5285,27 @@
       </c>
       <c r="AH40" t="inlineStr">
         <is>
-          <t>Högörtblandskog</t>
+          <t>Blåbärsblandskog</t>
         </is>
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5349,10 +5323,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118636848</v>
+        <v>118637923</v>
       </c>
       <c r="B41" t="n">
-        <v>79601</v>
+        <v>79608</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5392,10 +5366,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>529422</v>
+        <v>529679</v>
       </c>
       <c r="R41" t="n">
-        <v>7168348</v>
+        <v>7168420</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5442,17 +5416,17 @@
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
+          <t>Högörtblandskog</t>
         </is>
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
@@ -5462,7 +5436,7 @@
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5480,10 +5454,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118639270</v>
+        <v>118640655</v>
       </c>
       <c r="B42" t="n">
-        <v>79594</v>
+        <v>104932</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5496,26 +5470,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6462</v>
+        <v>221725</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5523,10 +5510,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>529596</v>
+        <v>529831</v>
       </c>
       <c r="R42" t="n">
-        <v>7168627</v>
+        <v>7168496</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5573,7 +5560,7 @@
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
+          <t>Högörtblandskog</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5591,10 +5578,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118639266</v>
+        <v>118640233</v>
       </c>
       <c r="B43" t="n">
-        <v>78484</v>
+        <v>79573</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5607,21 +5594,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5634,10 +5621,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>529596</v>
+        <v>529825</v>
       </c>
       <c r="R43" t="n">
-        <v>7168627</v>
+        <v>7168511</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5684,7 +5671,27 @@
       </c>
       <c r="AH43" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
+          <t>Högörtblandskog</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5702,10 +5709,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118637579</v>
+        <v>118638559</v>
       </c>
       <c r="B44" t="n">
-        <v>79601</v>
+        <v>78491</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5714,25 +5721,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5745,10 +5752,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>529657</v>
+        <v>529439</v>
       </c>
       <c r="R44" t="n">
-        <v>7168658</v>
+        <v>7168447</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5795,7 +5802,7 @@
       </c>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>Högörtblandskog</t>
+          <t>Blåbärsblandskog</t>
         </is>
       </c>
       <c r="AJ44" t="inlineStr">
@@ -5810,12 +5817,12 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5836,7 +5843,7 @@
         <v>118638509</v>
       </c>
       <c r="B45" t="n">
-        <v>79601</v>
+        <v>79608</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5964,10 +5971,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118637923</v>
+        <v>118637579</v>
       </c>
       <c r="B46" t="n">
-        <v>79601</v>
+        <v>79608</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6007,10 +6014,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>529679</v>
+        <v>529657</v>
       </c>
       <c r="R46" t="n">
-        <v>7168420</v>
+        <v>7168658</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -6072,12 +6079,12 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6095,10 +6102,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118638347</v>
+        <v>118638226</v>
       </c>
       <c r="B47" t="n">
-        <v>79601</v>
+        <v>79608</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6138,10 +6145,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>529581</v>
+        <v>529407</v>
       </c>
       <c r="R47" t="n">
-        <v>7168387</v>
+        <v>7168450</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -6226,10 +6233,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118639286</v>
+        <v>118638579</v>
       </c>
       <c r="B48" t="n">
-        <v>79565</v>
+        <v>79608</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6238,25 +6245,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6269,10 +6276,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>529596</v>
+        <v>529439</v>
       </c>
       <c r="R48" t="n">
-        <v>7168627</v>
+        <v>7168447</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -6316,11 +6323,6 @@
       <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -6337,7 +6339,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118638579</v>
+        <v>118640226</v>
       </c>
       <c r="B49" t="n">
         <v>79601</v>
@@ -6353,21 +6355,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6380,10 +6382,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>529439</v>
+        <v>529825</v>
       </c>
       <c r="R49" t="n">
-        <v>7168447</v>
+        <v>7168511</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -6427,6 +6429,31 @@
       <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>Högörtblandskog</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6446,7 +6473,7 @@
         <v>118638030</v>
       </c>
       <c r="B50" t="n">
-        <v>79601</v>
+        <v>79608</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6574,10 +6601,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>118638559</v>
+        <v>118640485</v>
       </c>
       <c r="B51" t="n">
-        <v>78484</v>
+        <v>104932</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6586,30 +6613,43 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>221725</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6617,10 +6657,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>529439</v>
+        <v>529812</v>
       </c>
       <c r="R51" t="n">
-        <v>7168447</v>
+        <v>7168477</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6667,27 +6707,7 @@
       </c>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Högörtblandskog</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6705,10 +6725,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>118638521</v>
+        <v>118637596</v>
       </c>
       <c r="B52" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6748,10 +6768,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>529374</v>
+        <v>529657</v>
       </c>
       <c r="R52" t="n">
-        <v>7168443</v>
+        <v>7168658</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6798,7 +6818,7 @@
       </c>
       <c r="AH52" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
+          <t>Högörtblandskog</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6816,10 +6836,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>118640233</v>
+        <v>118636851</v>
       </c>
       <c r="B53" t="n">
-        <v>79566</v>
+        <v>78491</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6832,21 +6852,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6859,10 +6879,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>529825</v>
+        <v>529422</v>
       </c>
       <c r="R53" t="n">
-        <v>7168511</v>
+        <v>7168348</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6909,27 +6929,7 @@
       </c>
       <c r="AH53" t="inlineStr">
         <is>
-          <t>Högörtblandskog</t>
-        </is>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Blåbärsblandskog</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>

--- a/artfynd/A 2227-2024 artfynd.xlsx
+++ b/artfynd/A 2227-2024 artfynd.xlsx
@@ -3173,10 +3173,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118376507</v>
+        <v>118376653</v>
       </c>
       <c r="B23" t="n">
-        <v>78491</v>
+        <v>104932</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3185,30 +3185,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>221725</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3216,10 +3229,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>529596</v>
+        <v>529335</v>
       </c>
       <c r="R23" t="n">
-        <v>7168313</v>
+        <v>7168411</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3284,7 +3297,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118376619</v>
+        <v>118376507</v>
       </c>
       <c r="B24" t="n">
         <v>78491</v>
@@ -3327,10 +3340,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>529335</v>
+        <v>529596</v>
       </c>
       <c r="R24" t="n">
-        <v>7168411</v>
+        <v>7168313</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3395,10 +3408,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118376653</v>
+        <v>118376619</v>
       </c>
       <c r="B25" t="n">
-        <v>104932</v>
+        <v>78491</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3407,43 +3420,30 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221725</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>

--- a/artfynd/A 2227-2024 artfynd.xlsx
+++ b/artfynd/A 2227-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118377695</v>
+        <v>118374825</v>
       </c>
       <c r="B2" t="n">
-        <v>79608</v>
+        <v>78491</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>529416</v>
+        <v>529615</v>
       </c>
       <c r="R2" t="n">
-        <v>7168380</v>
+        <v>7168654</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -768,27 +768,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Högörtblandskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -806,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118373894</v>
+        <v>118374787</v>
       </c>
       <c r="B3" t="n">
-        <v>97770</v>
+        <v>78491</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -818,43 +798,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -862,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>529729</v>
+        <v>529672</v>
       </c>
       <c r="R3" t="n">
-        <v>7168738</v>
+        <v>7168655</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -912,7 +879,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Blandsumpskog</t>
+          <t>Högörtblandskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -930,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118377198</v>
+        <v>118376493</v>
       </c>
       <c r="B4" t="n">
-        <v>98187</v>
+        <v>78491</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -942,43 +909,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219880</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -986,10 +940,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>529781</v>
+        <v>529564</v>
       </c>
       <c r="R4" t="n">
-        <v>7168708</v>
+        <v>7168298</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1036,7 +990,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Blandsumpskog</t>
+          <t>Blåbärsblandskog</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1054,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118374825</v>
+        <v>118377821</v>
       </c>
       <c r="B5" t="n">
-        <v>78491</v>
+        <v>79608</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1066,25 +1020,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1097,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>529615</v>
+        <v>529473</v>
       </c>
       <c r="R5" t="n">
-        <v>7168654</v>
+        <v>7168495</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1147,7 +1101,27 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Högörtblandskog</t>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1165,7 +1139,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118376316</v>
+        <v>118373990</v>
       </c>
       <c r="B6" t="n">
         <v>78491</v>
@@ -1208,10 +1182,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>529455</v>
+        <v>529729</v>
       </c>
       <c r="R6" t="n">
-        <v>7168453</v>
+        <v>7168738</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1258,7 +1232,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
+          <t>Blandsumpskog</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1276,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118374787</v>
+        <v>118374544</v>
       </c>
       <c r="B7" t="n">
-        <v>78491</v>
+        <v>97770</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1288,30 +1262,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1319,10 +1306,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>529672</v>
+        <v>529757</v>
       </c>
       <c r="R7" t="n">
-        <v>7168655</v>
+        <v>7168700</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1357,6 +1344,11 @@
           <t>2024-07-10</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>utan fläckar på bladen</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1369,7 +1361,7 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Högörtblandskog</t>
+          <t>Blandsumpskog</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1518,10 +1510,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118377115</v>
+        <v>118373653</v>
       </c>
       <c r="B9" t="n">
-        <v>98187</v>
+        <v>97770</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1534,26 +1526,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219880</v>
+        <v>219790</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1574,10 +1566,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>529828</v>
+        <v>529821</v>
       </c>
       <c r="R9" t="n">
-        <v>7168693</v>
+        <v>7168618</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1612,6 +1604,11 @@
           <t>2024-07-10</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>stort område med tät förekomst. Många med blad utan fläckar.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1621,11 +1618,6 @@
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Blandsumpskog</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1642,10 +1634,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118374393</v>
+        <v>118376886</v>
       </c>
       <c r="B10" t="n">
-        <v>97770</v>
+        <v>98187</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1658,26 +1650,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219790</v>
+        <v>219880</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1687,7 +1679,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
@@ -1698,10 +1690,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>529828</v>
+        <v>529825</v>
       </c>
       <c r="R10" t="n">
-        <v>7168707</v>
+        <v>7168680</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1734,11 +1726,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-07-10</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>mer eller mindre fläckiga blad</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1771,7 +1758,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118372553</v>
+        <v>118374393</v>
       </c>
       <c r="B11" t="n">
         <v>97770</v>
@@ -1806,7 +1793,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1827,10 +1814,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>529778</v>
+        <v>529828</v>
       </c>
       <c r="R11" t="n">
-        <v>7168467</v>
+        <v>7168707</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1863,6 +1850,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-07-10</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>mer eller mindre fläckiga blad</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1895,10 +1887,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118374544</v>
+        <v>118376521</v>
       </c>
       <c r="B12" t="n">
-        <v>97770</v>
+        <v>78491</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1907,43 +1899,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1951,10 +1930,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>529757</v>
+        <v>529657</v>
       </c>
       <c r="R12" t="n">
-        <v>7168700</v>
+        <v>7168427</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1989,11 +1968,6 @@
           <t>2024-07-10</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>utan fläckar på bladen</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2006,7 +1980,7 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Blandsumpskog</t>
+          <t>Blåbärsblandskog</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2259,10 +2233,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118376493</v>
+        <v>118372553</v>
       </c>
       <c r="B15" t="n">
-        <v>78491</v>
+        <v>97770</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2271,30 +2245,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2302,10 +2289,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>529564</v>
+        <v>529778</v>
       </c>
       <c r="R15" t="n">
-        <v>7168298</v>
+        <v>7168467</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2352,7 +2339,7 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
+          <t>Blandsumpskog</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2370,10 +2357,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118373990</v>
+        <v>118377198</v>
       </c>
       <c r="B16" t="n">
-        <v>78491</v>
+        <v>98187</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2382,30 +2369,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>219880</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>529729</v>
+        <v>529781</v>
       </c>
       <c r="R16" t="n">
-        <v>7168738</v>
+        <v>7168708</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2481,10 +2481,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118376553</v>
+        <v>118377497</v>
       </c>
       <c r="B17" t="n">
-        <v>78491</v>
+        <v>79608</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2493,25 +2493,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2524,10 +2524,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>529742</v>
+        <v>529366</v>
       </c>
       <c r="R17" t="n">
-        <v>7168447</v>
+        <v>7168437</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2574,7 +2574,27 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Blandsumpskog</t>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2592,10 +2612,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118376237</v>
+        <v>118377115</v>
       </c>
       <c r="B18" t="n">
-        <v>78491</v>
+        <v>98187</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2604,30 +2624,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>219880</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2635,10 +2668,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>529559</v>
+        <v>529828</v>
       </c>
       <c r="R18" t="n">
-        <v>7168596</v>
+        <v>7168693</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2685,7 +2718,7 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
+          <t>Blandsumpskog</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2703,7 +2736,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118376521</v>
+        <v>118376346</v>
       </c>
       <c r="B19" t="n">
         <v>78491</v>
@@ -2746,10 +2779,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>529657</v>
+        <v>529375</v>
       </c>
       <c r="R19" t="n">
-        <v>7168427</v>
+        <v>7168391</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2814,10 +2847,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118376346</v>
+        <v>118374116</v>
       </c>
       <c r="B20" t="n">
-        <v>78491</v>
+        <v>97770</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2826,30 +2859,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2857,10 +2903,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>529375</v>
+        <v>529691</v>
       </c>
       <c r="R20" t="n">
-        <v>7168391</v>
+        <v>7168682</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2907,7 +2953,7 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
+          <t>Blandsumpskog</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2925,7 +2971,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118373653</v>
+        <v>118373894</v>
       </c>
       <c r="B21" t="n">
         <v>97770</v>
@@ -2960,7 +3006,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2981,10 +3027,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>529821</v>
+        <v>529729</v>
       </c>
       <c r="R21" t="n">
-        <v>7168618</v>
+        <v>7168738</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -3019,11 +3065,6 @@
           <t>2024-07-10</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>stort område med tät förekomst. Många med blad utan fläckar.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3033,6 +3074,11 @@
       <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Blandsumpskog</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3049,7 +3095,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118374116</v>
+        <v>118372729</v>
       </c>
       <c r="B22" t="n">
         <v>97770</v>
@@ -3084,7 +3130,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3105,10 +3151,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>529691</v>
+        <v>529835</v>
       </c>
       <c r="R22" t="n">
-        <v>7168682</v>
+        <v>7168557</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3173,10 +3219,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118376653</v>
+        <v>118374699</v>
       </c>
       <c r="B23" t="n">
-        <v>104932</v>
+        <v>78491</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3185,43 +3231,30 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221725</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3229,10 +3262,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>529335</v>
+        <v>529749</v>
       </c>
       <c r="R23" t="n">
-        <v>7168411</v>
+        <v>7168733</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3279,7 +3312,7 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
+          <t>Blandsumpskog</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3297,10 +3330,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118376507</v>
+        <v>118373980</v>
       </c>
       <c r="B24" t="n">
-        <v>78491</v>
+        <v>98187</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3309,30 +3342,43 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>219880</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3340,10 +3386,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>529596</v>
+        <v>529729</v>
       </c>
       <c r="R24" t="n">
-        <v>7168313</v>
+        <v>7168738</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3390,7 +3436,7 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
+          <t>Blandsumpskog</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3408,7 +3454,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118376619</v>
+        <v>118376553</v>
       </c>
       <c r="B25" t="n">
         <v>78491</v>
@@ -3451,10 +3497,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>529335</v>
+        <v>529742</v>
       </c>
       <c r="R25" t="n">
-        <v>7168411</v>
+        <v>7168447</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3501,7 +3547,7 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
+          <t>Blandsumpskog</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3519,10 +3565,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118377821</v>
+        <v>118376237</v>
       </c>
       <c r="B26" t="n">
-        <v>79608</v>
+        <v>78491</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3531,25 +3577,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3562,10 +3608,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>529473</v>
+        <v>529559</v>
       </c>
       <c r="R26" t="n">
-        <v>7168495</v>
+        <v>7168596</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3613,26 +3659,6 @@
       <c r="AH26" t="inlineStr">
         <is>
           <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3761,10 +3787,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118373980</v>
+        <v>118376316</v>
       </c>
       <c r="B28" t="n">
-        <v>98187</v>
+        <v>78491</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3773,43 +3799,30 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219880</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3817,10 +3830,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>529729</v>
+        <v>529455</v>
       </c>
       <c r="R28" t="n">
-        <v>7168738</v>
+        <v>7168453</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3867,7 +3880,7 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Blandsumpskog</t>
+          <t>Blåbärsblandskog</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3885,7 +3898,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118374699</v>
+        <v>118376507</v>
       </c>
       <c r="B29" t="n">
         <v>78491</v>
@@ -3928,10 +3941,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>529749</v>
+        <v>529596</v>
       </c>
       <c r="R29" t="n">
-        <v>7168733</v>
+        <v>7168313</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3978,7 +3991,7 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Blandsumpskog</t>
+          <t>Blåbärsblandskog</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4107,10 +4120,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118376886</v>
+        <v>118377695</v>
       </c>
       <c r="B31" t="n">
-        <v>98187</v>
+        <v>79608</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4123,39 +4136,26 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>219880</v>
+        <v>6464</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr"/>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4163,10 +4163,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>529825</v>
+        <v>529416</v>
       </c>
       <c r="R31" t="n">
-        <v>7168680</v>
+        <v>7168380</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4213,7 +4213,27 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Blandsumpskog</t>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4231,10 +4251,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118372729</v>
+        <v>118376619</v>
       </c>
       <c r="B32" t="n">
-        <v>97770</v>
+        <v>78491</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4243,43 +4263,30 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4287,10 +4294,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>529835</v>
+        <v>529335</v>
       </c>
       <c r="R32" t="n">
-        <v>7168557</v>
+        <v>7168411</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4337,7 +4344,7 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>Blandsumpskog</t>
+          <t>Blåbärsblandskog</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4355,10 +4362,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118377497</v>
+        <v>118376653</v>
       </c>
       <c r="B33" t="n">
-        <v>79608</v>
+        <v>104932</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4371,26 +4378,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6464</v>
+        <v>221725</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4398,10 +4418,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>529366</v>
+        <v>529335</v>
       </c>
       <c r="R33" t="n">
-        <v>7168437</v>
+        <v>7168411</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4449,26 +4469,6 @@
       <c r="AH33" t="inlineStr">
         <is>
           <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4486,10 +4486,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118638521</v>
+        <v>118640655</v>
       </c>
       <c r="B34" t="n">
-        <v>78491</v>
+        <v>104932</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4498,30 +4498,43 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>221725</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4529,10 +4542,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>529374</v>
+        <v>529831</v>
       </c>
       <c r="R34" t="n">
-        <v>7168443</v>
+        <v>7168496</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4579,7 +4592,7 @@
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
+          <t>Högörtblandskog</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4597,10 +4610,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118639266</v>
+        <v>118638347</v>
       </c>
       <c r="B35" t="n">
-        <v>78491</v>
+        <v>79608</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4609,25 +4622,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4640,10 +4653,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>529596</v>
+        <v>529581</v>
       </c>
       <c r="R35" t="n">
-        <v>7168627</v>
+        <v>7168387</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4691,6 +4704,26 @@
       <c r="AH35" t="inlineStr">
         <is>
           <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4708,7 +4741,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118638993</v>
+        <v>118640226</v>
       </c>
       <c r="B36" t="n">
         <v>79601</v>
@@ -4751,10 +4784,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>529785</v>
+        <v>529825</v>
       </c>
       <c r="R36" t="n">
-        <v>7168501</v>
+        <v>7168511</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4816,12 +4849,12 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4839,10 +4872,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118639270</v>
+        <v>118638579</v>
       </c>
       <c r="B37" t="n">
-        <v>79601</v>
+        <v>79608</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4855,21 +4888,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4882,10 +4915,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>529596</v>
+        <v>529439</v>
       </c>
       <c r="R37" t="n">
-        <v>7168627</v>
+        <v>7168447</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4929,11 +4962,6 @@
       <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4950,10 +4978,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118639286</v>
+        <v>118638993</v>
       </c>
       <c r="B38" t="n">
-        <v>79572</v>
+        <v>79601</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4962,25 +4990,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4993,10 +5021,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>529596</v>
+        <v>529785</v>
       </c>
       <c r="R38" t="n">
-        <v>7168627</v>
+        <v>7168501</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -5043,7 +5071,27 @@
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
+          <t>Högörtblandskog</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5061,7 +5109,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118638347</v>
+        <v>118637923</v>
       </c>
       <c r="B39" t="n">
         <v>79608</v>
@@ -5104,10 +5152,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>529581</v>
+        <v>529679</v>
       </c>
       <c r="R39" t="n">
-        <v>7168387</v>
+        <v>7168420</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -5154,7 +5202,7 @@
       </c>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
+          <t>Högörtblandskog</t>
         </is>
       </c>
       <c r="AJ39" t="inlineStr">
@@ -5323,7 +5371,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118637923</v>
+        <v>118637579</v>
       </c>
       <c r="B41" t="n">
         <v>79608</v>
@@ -5366,10 +5414,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>529679</v>
+        <v>529657</v>
       </c>
       <c r="R41" t="n">
-        <v>7168420</v>
+        <v>7168658</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5431,12 +5479,12 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5454,10 +5502,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118640655</v>
+        <v>118639266</v>
       </c>
       <c r="B42" t="n">
-        <v>104932</v>
+        <v>78491</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5466,43 +5514,30 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221725</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5510,10 +5545,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>529831</v>
+        <v>529596</v>
       </c>
       <c r="R42" t="n">
-        <v>7168496</v>
+        <v>7168627</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5560,7 +5595,7 @@
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>Högörtblandskog</t>
+          <t>Blåbärsblandskog</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5578,10 +5613,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118640233</v>
+        <v>118640485</v>
       </c>
       <c r="B43" t="n">
-        <v>79573</v>
+        <v>104932</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5590,30 +5625,43 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2081</v>
+        <v>221725</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5621,10 +5669,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>529825</v>
+        <v>529812</v>
       </c>
       <c r="R43" t="n">
-        <v>7168511</v>
+        <v>7168477</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5672,26 +5720,6 @@
       <c r="AH43" t="inlineStr">
         <is>
           <t>Högörtblandskog</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5709,10 +5737,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118638559</v>
+        <v>118640233</v>
       </c>
       <c r="B44" t="n">
-        <v>78491</v>
+        <v>79573</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5725,21 +5753,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5752,10 +5780,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>529439</v>
+        <v>529825</v>
       </c>
       <c r="R44" t="n">
-        <v>7168447</v>
+        <v>7168511</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5802,7 +5830,7 @@
       </c>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
+          <t>Högörtblandskog</t>
         </is>
       </c>
       <c r="AJ44" t="inlineStr">
@@ -5817,12 +5845,12 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5840,7 +5868,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118638509</v>
+        <v>118638030</v>
       </c>
       <c r="B45" t="n">
         <v>79608</v>
@@ -5883,10 +5911,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>529374</v>
+        <v>529474</v>
       </c>
       <c r="R45" t="n">
-        <v>7168443</v>
+        <v>7168472</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5971,7 +5999,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118637579</v>
+        <v>118638509</v>
       </c>
       <c r="B46" t="n">
         <v>79608</v>
@@ -6014,10 +6042,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>529657</v>
+        <v>529374</v>
       </c>
       <c r="R46" t="n">
-        <v>7168658</v>
+        <v>7168443</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -6064,7 +6092,7 @@
       </c>
       <c r="AH46" t="inlineStr">
         <is>
-          <t>Högörtblandskog</t>
+          <t>Blåbärsblandskog</t>
         </is>
       </c>
       <c r="AJ46" t="inlineStr">
@@ -6079,12 +6107,12 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6233,10 +6261,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118638579</v>
+        <v>118636851</v>
       </c>
       <c r="B48" t="n">
-        <v>79608</v>
+        <v>78491</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6245,25 +6273,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6276,10 +6304,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>529439</v>
+        <v>529422</v>
       </c>
       <c r="R48" t="n">
-        <v>7168447</v>
+        <v>7168348</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -6323,6 +6351,11 @@
       <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -6339,10 +6372,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118640226</v>
+        <v>118638559</v>
       </c>
       <c r="B49" t="n">
-        <v>79601</v>
+        <v>78491</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6351,25 +6384,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6382,10 +6415,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>529825</v>
+        <v>529439</v>
       </c>
       <c r="R49" t="n">
-        <v>7168511</v>
+        <v>7168447</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -6432,7 +6465,7 @@
       </c>
       <c r="AH49" t="inlineStr">
         <is>
-          <t>Högörtblandskog</t>
+          <t>Blåbärsblandskog</t>
         </is>
       </c>
       <c r="AJ49" t="inlineStr">
@@ -6447,12 +6480,12 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6470,10 +6503,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118638030</v>
+        <v>118638521</v>
       </c>
       <c r="B50" t="n">
-        <v>79608</v>
+        <v>78491</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6482,25 +6515,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6513,10 +6546,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>529474</v>
+        <v>529374</v>
       </c>
       <c r="R50" t="n">
-        <v>7168472</v>
+        <v>7168443</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6564,26 +6597,6 @@
       <c r="AH50" t="inlineStr">
         <is>
           <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6601,10 +6614,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>118640485</v>
+        <v>118637596</v>
       </c>
       <c r="B51" t="n">
-        <v>104932</v>
+        <v>78491</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6613,43 +6626,30 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221725</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6657,10 +6657,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>529812</v>
+        <v>529657</v>
       </c>
       <c r="R51" t="n">
-        <v>7168477</v>
+        <v>7168658</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6725,10 +6725,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>118637596</v>
+        <v>118639286</v>
       </c>
       <c r="B52" t="n">
-        <v>78491</v>
+        <v>79572</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6741,21 +6741,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6768,10 +6768,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>529657</v>
+        <v>529596</v>
       </c>
       <c r="R52" t="n">
-        <v>7168658</v>
+        <v>7168627</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6818,7 +6818,7 @@
       </c>
       <c r="AH52" t="inlineStr">
         <is>
-          <t>Högörtblandskog</t>
+          <t>Blåbärsblandskog</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6836,10 +6836,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>118636851</v>
+        <v>118639270</v>
       </c>
       <c r="B53" t="n">
-        <v>78491</v>
+        <v>79601</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6848,25 +6848,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6879,10 +6879,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>529422</v>
+        <v>529596</v>
       </c>
       <c r="R53" t="n">
-        <v>7168348</v>
+        <v>7168627</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>

--- a/artfynd/A 2227-2024 artfynd.xlsx
+++ b/artfynd/A 2227-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY53"/>
+  <dimension ref="A1:AY73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6945,6 +6945,2051 @@
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>120416764</v>
+      </c>
+      <c r="B54" t="n">
+        <v>79652</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Storbäck, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>529692</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7168426</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Elijah Ourth</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Elijah Ourth</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>120417044</v>
+      </c>
+      <c r="B55" t="n">
+        <v>79623</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Hundsjökullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>529593</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7168634</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Elijah Ourth</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>120416882</v>
+      </c>
+      <c r="B56" t="n">
+        <v>90580</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Vaerie Plaajhkije, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>529418</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7168461</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Elijah Ourth</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Elijah Ourth</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>120416943</v>
+      </c>
+      <c r="B57" t="n">
+        <v>90598</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Vaerie Plaajhkije, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>529481</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7168384</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Elijah Ourth</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Elijah Ourth</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>120417046</v>
+      </c>
+      <c r="B58" t="n">
+        <v>79659</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Hundsjökullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>529775</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7168673</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Elijah Ourth</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>120417040</v>
+      </c>
+      <c r="B59" t="n">
+        <v>94334</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>2809</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Mörk husmossa</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Hundsjökullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>529677</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7168627</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Elijah Ourth</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>120417039</v>
+      </c>
+      <c r="B60" t="n">
+        <v>94334</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>2809</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Mörk husmossa</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Hundsjökullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>529794</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7168678</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Elijah Ourth</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>120416985</v>
+      </c>
+      <c r="B61" t="n">
+        <v>57473</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Hundsjökullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>529478</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7168453</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Elijah Ourth</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>120417149</v>
+      </c>
+      <c r="B62" t="n">
+        <v>79658</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Hundsjökullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>529593</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7168634</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Elijah Ourth</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>120417071</v>
+      </c>
+      <c r="B63" t="n">
+        <v>56524</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Hundsjökullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>529795</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7168678</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Elijah Ourth</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>120416775</v>
+      </c>
+      <c r="B64" t="n">
+        <v>79623</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Storbäck, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>529631</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7168396</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Elijah Ourth</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Elijah Ourth</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>120417056</v>
+      </c>
+      <c r="B65" t="n">
+        <v>93958</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>2387</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Källpraktmossa</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Pseudobryum cinclidioides</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Huebener) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Hundsjökullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>529775</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7168673</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Elijah Ourth</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>120417058</v>
+      </c>
+      <c r="B66" t="n">
+        <v>98265</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>219880</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Kransrams</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Polygonatum verticillatum</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Hundsjökullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>529723</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7168608</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Elijah Ourth</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>120417097</v>
+      </c>
+      <c r="B67" t="n">
+        <v>90598</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Hundsjökullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>529628</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7168643</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Elijah Ourth</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>120417080</v>
+      </c>
+      <c r="B68" t="n">
+        <v>90594</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Hundsjökullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>529451</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7168444</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Elijah Ourth</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>120416902</v>
+      </c>
+      <c r="B69" t="n">
+        <v>79652</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Vaerie Plaajhkije, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>529607</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7168510</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Elijah Ourth</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Elijah Ourth</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>120417012</v>
+      </c>
+      <c r="B70" t="n">
+        <v>79624</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Hundsjökullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>529686</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7168621</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Elijah Ourth</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>120417041</v>
+      </c>
+      <c r="B71" t="n">
+        <v>94334</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>2809</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Mörk husmossa</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Hundsjökullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>529692</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7168631</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Elijah Ourth</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>120417070</v>
+      </c>
+      <c r="B72" t="n">
+        <v>56524</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Hundsjökullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>529723</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7168608</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Elijah Ourth</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>120416964</v>
+      </c>
+      <c r="B73" t="n">
+        <v>90545</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Hundsjökullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>529779</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7168668</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Elijah Ourth</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 2227-2024 artfynd.xlsx
+++ b/artfynd/A 2227-2024 artfynd.xlsx
@@ -6947,10 +6947,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120416764</v>
+        <v>120417039</v>
       </c>
       <c r="B54" t="n">
-        <v>79652</v>
+        <v>94334</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6963,34 +6963,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6462</v>
+        <v>2809</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Storbäck, Ås lm</t>
+          <t>Hundsjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>529692</v>
+        <v>529794</v>
       </c>
       <c r="R54" t="n">
-        <v>7168426</v>
+        <v>7168678</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7017,12 +7017,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7042,17 +7042,17 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Elijah Ourth</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120417044</v>
+        <v>120416882</v>
       </c>
       <c r="B55" t="n">
-        <v>79623</v>
+        <v>90580</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7065,34 +7065,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Hundsjökullen, Ås lm</t>
+          <t>Vaerie Plaajhkije, Ås lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>529593</v>
+        <v>529418</v>
       </c>
       <c r="R55" t="n">
-        <v>7168634</v>
+        <v>7168461</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7144,17 +7144,17 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Elijah Ourth</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120416882</v>
+        <v>120417012</v>
       </c>
       <c r="B56" t="n">
-        <v>90580</v>
+        <v>79624</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7167,34 +7167,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Vaerie Plaajhkije, Ås lm</t>
+          <t>Hundsjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>529418</v>
+        <v>529686</v>
       </c>
       <c r="R56" t="n">
-        <v>7168461</v>
+        <v>7168621</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7246,17 +7246,17 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Elijah Ourth</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120416943</v>
+        <v>120417044</v>
       </c>
       <c r="B57" t="n">
-        <v>90598</v>
+        <v>79623</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7269,34 +7269,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Vaerie Plaajhkije, Ås lm</t>
+          <t>Hundsjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>529481</v>
+        <v>529593</v>
       </c>
       <c r="R57" t="n">
-        <v>7168384</v>
+        <v>7168634</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7348,17 +7348,17 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Elijah Ourth</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120417046</v>
+        <v>120416902</v>
       </c>
       <c r="B58" t="n">
-        <v>79659</v>
+        <v>79652</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7371,34 +7371,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Hundsjökullen, Ås lm</t>
+          <t>Vaerie Plaajhkije, Ås lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>529775</v>
+        <v>529607</v>
       </c>
       <c r="R58" t="n">
-        <v>7168673</v>
+        <v>7168510</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7450,17 +7450,17 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Elijah Ourth</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120417040</v>
+        <v>120417070</v>
       </c>
       <c r="B59" t="n">
-        <v>94334</v>
+        <v>56524</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7469,25 +7469,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2809</v>
+        <v>102612</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7497,10 +7497,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>529677</v>
+        <v>529723</v>
       </c>
       <c r="R59" t="n">
-        <v>7168627</v>
+        <v>7168608</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7559,10 +7559,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120417039</v>
+        <v>120417056</v>
       </c>
       <c r="B60" t="n">
-        <v>94334</v>
+        <v>93958</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7575,21 +7575,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2809</v>
+        <v>2387</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7599,10 +7599,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>529794</v>
+        <v>529775</v>
       </c>
       <c r="R60" t="n">
-        <v>7168678</v>
+        <v>7168673</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7661,10 +7661,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120416985</v>
+        <v>120417040</v>
       </c>
       <c r="B61" t="n">
-        <v>57473</v>
+        <v>94334</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7673,43 +7673,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>103021</v>
+        <v>2809</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Hundsjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>529478</v>
+        <v>529677</v>
       </c>
       <c r="R61" t="n">
-        <v>7168453</v>
+        <v>7168627</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7768,10 +7763,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120417149</v>
+        <v>120416964</v>
       </c>
       <c r="B62" t="n">
-        <v>79658</v>
+        <v>90545</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7784,21 +7779,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6463</v>
+        <v>5447</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7808,10 +7803,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>529593</v>
+        <v>529779</v>
       </c>
       <c r="R62" t="n">
-        <v>7168634</v>
+        <v>7168668</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7870,10 +7865,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120417071</v>
+        <v>120417058</v>
       </c>
       <c r="B63" t="n">
-        <v>56524</v>
+        <v>98265</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7882,25 +7877,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>102612</v>
+        <v>219880</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7910,10 +7905,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>529795</v>
+        <v>529723</v>
       </c>
       <c r="R63" t="n">
-        <v>7168678</v>
+        <v>7168608</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7972,10 +7967,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120416775</v>
+        <v>120417071</v>
       </c>
       <c r="B64" t="n">
-        <v>79623</v>
+        <v>56524</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7988,34 +7983,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Storbäck, Ås lm</t>
+          <t>Hundsjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>529631</v>
+        <v>529795</v>
       </c>
       <c r="R64" t="n">
-        <v>7168396</v>
+        <v>7168678</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8042,12 +8037,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8067,17 +8062,17 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Elijah Ourth</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120417056</v>
+        <v>120416943</v>
       </c>
       <c r="B65" t="n">
-        <v>93958</v>
+        <v>90598</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8086,38 +8081,38 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2387</v>
+        <v>5432</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Hundsjökullen, Ås lm</t>
+          <t>Vaerie Plaajhkije, Ås lm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>529775</v>
+        <v>529481</v>
       </c>
       <c r="R65" t="n">
-        <v>7168673</v>
+        <v>7168384</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8169,17 +8164,17 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Elijah Ourth</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120417058</v>
+        <v>120417041</v>
       </c>
       <c r="B66" t="n">
-        <v>98265</v>
+        <v>94334</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8192,21 +8187,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>219880</v>
+        <v>2809</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8216,10 +8211,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>529723</v>
+        <v>529692</v>
       </c>
       <c r="R66" t="n">
-        <v>7168608</v>
+        <v>7168631</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8380,10 +8375,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120417080</v>
+        <v>120417046</v>
       </c>
       <c r="B68" t="n">
-        <v>90594</v>
+        <v>79659</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8392,25 +8387,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1204</v>
+        <v>6464</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8420,10 +8415,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>529451</v>
+        <v>529775</v>
       </c>
       <c r="R68" t="n">
-        <v>7168444</v>
+        <v>7168673</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8482,10 +8477,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120416902</v>
+        <v>120416985</v>
       </c>
       <c r="B69" t="n">
-        <v>79652</v>
+        <v>57473</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8494,38 +8489,43 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6462</v>
+        <v>103021</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Vaerie Plaajhkije, Ås lm</t>
+          <t>Hundsjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>529607</v>
+        <v>529478</v>
       </c>
       <c r="R69" t="n">
-        <v>7168510</v>
+        <v>7168453</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8577,17 +8577,17 @@
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Elijah Ourth</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120417012</v>
+        <v>120416764</v>
       </c>
       <c r="B70" t="n">
-        <v>79624</v>
+        <v>79652</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8596,38 +8596,38 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Hundsjökullen, Ås lm</t>
+          <t>Storbäck, Ås lm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>529686</v>
+        <v>529692</v>
       </c>
       <c r="R70" t="n">
-        <v>7168621</v>
+        <v>7168426</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8654,12 +8654,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8679,17 +8679,17 @@
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Elijah Ourth</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120417041</v>
+        <v>120417149</v>
       </c>
       <c r="B71" t="n">
-        <v>94334</v>
+        <v>79658</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8702,21 +8702,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2809</v>
+        <v>6463</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8726,10 +8726,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>529692</v>
+        <v>529593</v>
       </c>
       <c r="R71" t="n">
-        <v>7168631</v>
+        <v>7168634</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8788,10 +8788,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120417070</v>
+        <v>120416775</v>
       </c>
       <c r="B72" t="n">
-        <v>56524</v>
+        <v>79623</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8804,34 +8804,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Hundsjökullen, Ås lm</t>
+          <t>Storbäck, Ås lm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>529723</v>
+        <v>529631</v>
       </c>
       <c r="R72" t="n">
-        <v>7168608</v>
+        <v>7168396</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8858,12 +8858,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8883,17 +8883,17 @@
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Elijah Ourth</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120416964</v>
+        <v>120417080</v>
       </c>
       <c r="B73" t="n">
-        <v>90545</v>
+        <v>90594</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8902,25 +8902,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5447</v>
+        <v>1204</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8930,10 +8930,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>529779</v>
+        <v>529451</v>
       </c>
       <c r="R73" t="n">
-        <v>7168668</v>
+        <v>7168444</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>

--- a/artfynd/A 2227-2024 artfynd.xlsx
+++ b/artfynd/A 2227-2024 artfynd.xlsx
@@ -6947,10 +6947,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120417039</v>
+        <v>120417056</v>
       </c>
       <c r="B54" t="n">
-        <v>94334</v>
+        <v>93958</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6963,21 +6963,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2809</v>
+        <v>2387</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6987,10 +6987,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>529794</v>
+        <v>529775</v>
       </c>
       <c r="R54" t="n">
-        <v>7168678</v>
+        <v>7168673</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7049,10 +7049,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120416882</v>
+        <v>120417058</v>
       </c>
       <c r="B55" t="n">
-        <v>90580</v>
+        <v>98265</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7061,38 +7061,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>219880</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Vaerie Plaajhkije, Ås lm</t>
+          <t>Hundsjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>529418</v>
+        <v>529723</v>
       </c>
       <c r="R55" t="n">
-        <v>7168461</v>
+        <v>7168608</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7144,17 +7144,17 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Elijah Ourth</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120417012</v>
+        <v>120417149</v>
       </c>
       <c r="B56" t="n">
-        <v>79624</v>
+        <v>79658</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7163,25 +7163,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7191,10 +7191,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>529686</v>
+        <v>529593</v>
       </c>
       <c r="R56" t="n">
-        <v>7168621</v>
+        <v>7168634</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7253,10 +7253,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120417044</v>
+        <v>120417041</v>
       </c>
       <c r="B57" t="n">
-        <v>79623</v>
+        <v>94334</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7265,25 +7265,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>2809</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7293,10 +7293,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>529593</v>
+        <v>529692</v>
       </c>
       <c r="R57" t="n">
-        <v>7168634</v>
+        <v>7168631</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7355,7 +7355,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120416902</v>
+        <v>120416764</v>
       </c>
       <c r="B58" t="n">
         <v>79652</v>
@@ -7391,14 +7391,14 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Vaerie Plaajhkije, Ås lm</t>
+          <t>Storbäck, Ås lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>529607</v>
+        <v>529692</v>
       </c>
       <c r="R58" t="n">
-        <v>7168510</v>
+        <v>7168426</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7425,12 +7425,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7457,10 +7457,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120417070</v>
+        <v>120417040</v>
       </c>
       <c r="B59" t="n">
-        <v>56524</v>
+        <v>94334</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7469,25 +7469,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>102612</v>
+        <v>2809</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7497,10 +7497,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>529723</v>
+        <v>529677</v>
       </c>
       <c r="R59" t="n">
-        <v>7168608</v>
+        <v>7168627</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7559,10 +7559,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120417056</v>
+        <v>120417044</v>
       </c>
       <c r="B60" t="n">
-        <v>93958</v>
+        <v>79623</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7571,25 +7571,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2387</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7599,10 +7599,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>529775</v>
+        <v>529593</v>
       </c>
       <c r="R60" t="n">
-        <v>7168673</v>
+        <v>7168634</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7661,10 +7661,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120417040</v>
+        <v>120417070</v>
       </c>
       <c r="B61" t="n">
-        <v>94334</v>
+        <v>56524</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7673,25 +7673,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2809</v>
+        <v>102612</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7701,10 +7701,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>529677</v>
+        <v>529723</v>
       </c>
       <c r="R61" t="n">
-        <v>7168627</v>
+        <v>7168608</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7763,10 +7763,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120416964</v>
+        <v>120416775</v>
       </c>
       <c r="B62" t="n">
-        <v>90545</v>
+        <v>79623</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7775,38 +7775,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Hundsjökullen, Ås lm</t>
+          <t>Storbäck, Ås lm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>529779</v>
+        <v>529631</v>
       </c>
       <c r="R62" t="n">
-        <v>7168668</v>
+        <v>7168396</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7858,17 +7858,17 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Elijah Ourth</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120417058</v>
+        <v>120416964</v>
       </c>
       <c r="B63" t="n">
-        <v>98265</v>
+        <v>90545</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7881,21 +7881,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>219880</v>
+        <v>5447</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7905,10 +7905,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>529723</v>
+        <v>529779</v>
       </c>
       <c r="R63" t="n">
-        <v>7168608</v>
+        <v>7168668</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7967,10 +7967,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120417071</v>
+        <v>120416985</v>
       </c>
       <c r="B64" t="n">
-        <v>56524</v>
+        <v>57473</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7983,34 +7983,39 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>102612</v>
+        <v>103021</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Hundsjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>529795</v>
+        <v>529478</v>
       </c>
       <c r="R64" t="n">
-        <v>7168678</v>
+        <v>7168453</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8069,10 +8074,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120416943</v>
+        <v>120417080</v>
       </c>
       <c r="B65" t="n">
-        <v>90598</v>
+        <v>90594</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8085,34 +8090,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Vaerie Plaajhkije, Ås lm</t>
+          <t>Hundsjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>529481</v>
+        <v>529451</v>
       </c>
       <c r="R65" t="n">
-        <v>7168384</v>
+        <v>7168444</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8164,17 +8169,17 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Elijah Ourth</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120417041</v>
+        <v>120416902</v>
       </c>
       <c r="B66" t="n">
-        <v>94334</v>
+        <v>79652</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8187,34 +8192,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2809</v>
+        <v>6462</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Hundsjökullen, Ås lm</t>
+          <t>Vaerie Plaajhkije, Ås lm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>529692</v>
+        <v>529607</v>
       </c>
       <c r="R66" t="n">
-        <v>7168631</v>
+        <v>7168510</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8266,14 +8271,14 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Elijah Ourth</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120417097</v>
+        <v>120416943</v>
       </c>
       <c r="B67" t="n">
         <v>90598</v>
@@ -8309,14 +8314,14 @@
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Hundsjökullen, Ås lm</t>
+          <t>Vaerie Plaajhkije, Ås lm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>529628</v>
+        <v>529481</v>
       </c>
       <c r="R67" t="n">
-        <v>7168643</v>
+        <v>7168384</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8368,7 +8373,7 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Elijah Ourth</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -8477,10 +8482,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120416985</v>
+        <v>120416882</v>
       </c>
       <c r="B69" t="n">
-        <v>57473</v>
+        <v>90580</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8493,39 +8498,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Hundsjökullen, Ås lm</t>
+          <t>Vaerie Plaajhkije, Ås lm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>529478</v>
+        <v>529418</v>
       </c>
       <c r="R69" t="n">
-        <v>7168453</v>
+        <v>7168461</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8577,17 +8577,17 @@
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Elijah Ourth</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120416764</v>
+        <v>120417039</v>
       </c>
       <c r="B70" t="n">
-        <v>79652</v>
+        <v>94334</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8600,34 +8600,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6462</v>
+        <v>2809</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Storbäck, Ås lm</t>
+          <t>Hundsjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>529692</v>
+        <v>529794</v>
       </c>
       <c r="R70" t="n">
-        <v>7168426</v>
+        <v>7168678</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8654,12 +8654,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8679,17 +8679,17 @@
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Elijah Ourth</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120417149</v>
+        <v>120417012</v>
       </c>
       <c r="B71" t="n">
-        <v>79658</v>
+        <v>79624</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8698,25 +8698,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8726,10 +8726,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>529593</v>
+        <v>529686</v>
       </c>
       <c r="R71" t="n">
-        <v>7168634</v>
+        <v>7168621</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8788,10 +8788,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120416775</v>
+        <v>120417097</v>
       </c>
       <c r="B72" t="n">
-        <v>79623</v>
+        <v>90598</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8804,34 +8804,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Storbäck, Ås lm</t>
+          <t>Hundsjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>529631</v>
+        <v>529628</v>
       </c>
       <c r="R72" t="n">
-        <v>7168396</v>
+        <v>7168643</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8858,12 +8858,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8883,17 +8883,17 @@
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Elijah Ourth</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120417080</v>
+        <v>120417071</v>
       </c>
       <c r="B73" t="n">
-        <v>90594</v>
+        <v>56524</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8906,21 +8906,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1204</v>
+        <v>102612</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8930,10 +8930,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>529451</v>
+        <v>529795</v>
       </c>
       <c r="R73" t="n">
-        <v>7168444</v>
+        <v>7168678</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>

--- a/artfynd/A 2227-2024 artfynd.xlsx
+++ b/artfynd/A 2227-2024 artfynd.xlsx
@@ -6947,10 +6947,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120417056</v>
+        <v>120416775</v>
       </c>
       <c r="B54" t="n">
-        <v>93958</v>
+        <v>79623</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6959,38 +6959,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2387</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Hundsjökullen, Ås lm</t>
+          <t>Storbäck, Ås lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>529775</v>
+        <v>529631</v>
       </c>
       <c r="R54" t="n">
-        <v>7168673</v>
+        <v>7168396</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7017,12 +7017,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7042,17 +7042,17 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Elijah Ourth</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120417058</v>
+        <v>120417056</v>
       </c>
       <c r="B55" t="n">
-        <v>98265</v>
+        <v>93958</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7065,21 +7065,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>219880</v>
+        <v>2387</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -7089,10 +7089,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>529723</v>
+        <v>529775</v>
       </c>
       <c r="R55" t="n">
-        <v>7168608</v>
+        <v>7168673</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7151,10 +7151,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120417149</v>
+        <v>120417040</v>
       </c>
       <c r="B56" t="n">
-        <v>79658</v>
+        <v>94334</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7167,21 +7167,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6463</v>
+        <v>2809</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7191,10 +7191,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>529593</v>
+        <v>529677</v>
       </c>
       <c r="R56" t="n">
-        <v>7168634</v>
+        <v>7168627</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7253,10 +7253,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120417041</v>
+        <v>120417097</v>
       </c>
       <c r="B57" t="n">
-        <v>94334</v>
+        <v>90598</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7265,25 +7265,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2809</v>
+        <v>5432</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7293,10 +7293,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>529692</v>
+        <v>529628</v>
       </c>
       <c r="R57" t="n">
-        <v>7168631</v>
+        <v>7168643</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7355,10 +7355,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120416764</v>
+        <v>120417071</v>
       </c>
       <c r="B58" t="n">
-        <v>79652</v>
+        <v>56524</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7367,38 +7367,38 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6462</v>
+        <v>102612</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Storbäck, Ås lm</t>
+          <t>Hundsjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>529692</v>
+        <v>529795</v>
       </c>
       <c r="R58" t="n">
-        <v>7168426</v>
+        <v>7168678</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7425,12 +7425,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7450,17 +7450,17 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Elijah Ourth</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120417040</v>
+        <v>120416985</v>
       </c>
       <c r="B59" t="n">
-        <v>94334</v>
+        <v>57473</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7469,38 +7469,43 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2809</v>
+        <v>103021</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Hundsjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>529677</v>
+        <v>529478</v>
       </c>
       <c r="R59" t="n">
-        <v>7168627</v>
+        <v>7168453</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7559,10 +7564,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120417044</v>
+        <v>120417039</v>
       </c>
       <c r="B60" t="n">
-        <v>79623</v>
+        <v>94334</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7571,25 +7576,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>2809</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7599,10 +7604,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>529593</v>
+        <v>529794</v>
       </c>
       <c r="R60" t="n">
-        <v>7168634</v>
+        <v>7168678</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7661,10 +7666,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120417070</v>
+        <v>120417080</v>
       </c>
       <c r="B61" t="n">
-        <v>56524</v>
+        <v>90594</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7677,21 +7682,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>102612</v>
+        <v>1204</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7701,10 +7706,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>529723</v>
+        <v>529451</v>
       </c>
       <c r="R61" t="n">
-        <v>7168608</v>
+        <v>7168444</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7763,10 +7768,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120416775</v>
+        <v>120416882</v>
       </c>
       <c r="B62" t="n">
-        <v>79623</v>
+        <v>90580</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7779,34 +7784,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Storbäck, Ås lm</t>
+          <t>Vaerie Plaajhkije, Ås lm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>529631</v>
+        <v>529418</v>
       </c>
       <c r="R62" t="n">
-        <v>7168396</v>
+        <v>7168461</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7833,12 +7838,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7865,10 +7870,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120416964</v>
+        <v>120417070</v>
       </c>
       <c r="B63" t="n">
-        <v>90545</v>
+        <v>56524</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7877,25 +7882,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5447</v>
+        <v>102612</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7905,10 +7910,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>529779</v>
+        <v>529723</v>
       </c>
       <c r="R63" t="n">
-        <v>7168668</v>
+        <v>7168608</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7967,10 +7972,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120416985</v>
+        <v>120417058</v>
       </c>
       <c r="B64" t="n">
-        <v>57473</v>
+        <v>98265</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7979,43 +7984,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>103021</v>
+        <v>219880</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Hundsjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>529478</v>
+        <v>529723</v>
       </c>
       <c r="R64" t="n">
-        <v>7168453</v>
+        <v>7168608</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8074,10 +8074,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120417080</v>
+        <v>120416943</v>
       </c>
       <c r="B65" t="n">
-        <v>90594</v>
+        <v>90598</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8090,34 +8090,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Hundsjökullen, Ås lm</t>
+          <t>Vaerie Plaajhkije, Ås lm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>529451</v>
+        <v>529481</v>
       </c>
       <c r="R65" t="n">
-        <v>7168444</v>
+        <v>7168384</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8169,17 +8169,17 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Elijah Ourth</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120416902</v>
+        <v>120417012</v>
       </c>
       <c r="B66" t="n">
-        <v>79652</v>
+        <v>79624</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8188,38 +8188,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Vaerie Plaajhkije, Ås lm</t>
+          <t>Hundsjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>529607</v>
+        <v>529686</v>
       </c>
       <c r="R66" t="n">
-        <v>7168510</v>
+        <v>7168621</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8271,17 +8271,17 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Elijah Ourth</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120416943</v>
+        <v>120416764</v>
       </c>
       <c r="B67" t="n">
-        <v>90598</v>
+        <v>79652</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8290,38 +8290,38 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Vaerie Plaajhkije, Ås lm</t>
+          <t>Storbäck, Ås lm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>529481</v>
+        <v>529692</v>
       </c>
       <c r="R67" t="n">
-        <v>7168384</v>
+        <v>7168426</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8348,12 +8348,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8380,10 +8380,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120417046</v>
+        <v>120417044</v>
       </c>
       <c r="B68" t="n">
-        <v>79659</v>
+        <v>79623</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8392,25 +8392,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8420,10 +8420,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>529775</v>
+        <v>529593</v>
       </c>
       <c r="R68" t="n">
-        <v>7168673</v>
+        <v>7168634</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8482,10 +8482,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120416882</v>
+        <v>120416964</v>
       </c>
       <c r="B69" t="n">
-        <v>90580</v>
+        <v>90545</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8494,38 +8494,38 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Vaerie Plaajhkije, Ås lm</t>
+          <t>Hundsjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>529418</v>
+        <v>529779</v>
       </c>
       <c r="R69" t="n">
-        <v>7168461</v>
+        <v>7168668</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8577,14 +8577,14 @@
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Elijah Ourth</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120417039</v>
+        <v>120417041</v>
       </c>
       <c r="B70" t="n">
         <v>94334</v>
@@ -8624,10 +8624,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>529794</v>
+        <v>529692</v>
       </c>
       <c r="R70" t="n">
-        <v>7168678</v>
+        <v>7168631</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8686,10 +8686,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120417012</v>
+        <v>120417046</v>
       </c>
       <c r="B71" t="n">
-        <v>79624</v>
+        <v>79659</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8698,25 +8698,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8726,10 +8726,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>529686</v>
+        <v>529775</v>
       </c>
       <c r="R71" t="n">
-        <v>7168621</v>
+        <v>7168673</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8788,10 +8788,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120417097</v>
+        <v>120416902</v>
       </c>
       <c r="B72" t="n">
-        <v>90598</v>
+        <v>79652</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8800,38 +8800,38 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Hundsjökullen, Ås lm</t>
+          <t>Vaerie Plaajhkije, Ås lm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>529628</v>
+        <v>529607</v>
       </c>
       <c r="R72" t="n">
-        <v>7168643</v>
+        <v>7168510</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8883,17 +8883,17 @@
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Elijah Ourth</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120417071</v>
+        <v>120417149</v>
       </c>
       <c r="B73" t="n">
-        <v>56524</v>
+        <v>79658</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8902,25 +8902,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>102612</v>
+        <v>6463</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8930,10 +8930,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>529795</v>
+        <v>529593</v>
       </c>
       <c r="R73" t="n">
-        <v>7168678</v>
+        <v>7168634</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>

--- a/artfynd/A 2227-2024 artfynd.xlsx
+++ b/artfynd/A 2227-2024 artfynd.xlsx
@@ -7457,10 +7457,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120416985</v>
+        <v>120417039</v>
       </c>
       <c r="B59" t="n">
-        <v>57473</v>
+        <v>94334</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7469,43 +7469,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>103021</v>
+        <v>2809</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Hundsjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>529478</v>
+        <v>529794</v>
       </c>
       <c r="R59" t="n">
-        <v>7168453</v>
+        <v>7168678</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7564,10 +7559,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120417039</v>
+        <v>120416985</v>
       </c>
       <c r="B60" t="n">
-        <v>94334</v>
+        <v>57473</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7576,38 +7571,43 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2809</v>
+        <v>103021</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Hundsjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>529794</v>
+        <v>529478</v>
       </c>
       <c r="R60" t="n">
-        <v>7168678</v>
+        <v>7168453</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7666,10 +7666,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120417080</v>
+        <v>120417070</v>
       </c>
       <c r="B61" t="n">
-        <v>90594</v>
+        <v>56524</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7682,21 +7682,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1204</v>
+        <v>102612</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7706,10 +7706,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>529451</v>
+        <v>529723</v>
       </c>
       <c r="R61" t="n">
-        <v>7168444</v>
+        <v>7168608</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7768,10 +7768,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120416882</v>
+        <v>120417058</v>
       </c>
       <c r="B62" t="n">
-        <v>90580</v>
+        <v>98265</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7780,38 +7780,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>219880</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Vaerie Plaajhkije, Ås lm</t>
+          <t>Hundsjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>529418</v>
+        <v>529723</v>
       </c>
       <c r="R62" t="n">
-        <v>7168461</v>
+        <v>7168608</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7863,17 +7863,17 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Elijah Ourth</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120417070</v>
+        <v>120417080</v>
       </c>
       <c r="B63" t="n">
-        <v>56524</v>
+        <v>90594</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7886,21 +7886,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>102612</v>
+        <v>1204</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7910,10 +7910,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>529723</v>
+        <v>529451</v>
       </c>
       <c r="R63" t="n">
-        <v>7168608</v>
+        <v>7168444</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7972,10 +7972,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120417058</v>
+        <v>120416882</v>
       </c>
       <c r="B64" t="n">
-        <v>98265</v>
+        <v>90580</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7984,38 +7984,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>219880</v>
+        <v>1202</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Hundsjökullen, Ås lm</t>
+          <t>Vaerie Plaajhkije, Ås lm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>529723</v>
+        <v>529418</v>
       </c>
       <c r="R64" t="n">
-        <v>7168608</v>
+        <v>7168461</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8067,7 +8067,7 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Elijah Ourth</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
@@ -8380,10 +8380,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120417044</v>
+        <v>120417041</v>
       </c>
       <c r="B68" t="n">
-        <v>79623</v>
+        <v>94334</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8392,25 +8392,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>2809</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8420,10 +8420,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>529593</v>
+        <v>529692</v>
       </c>
       <c r="R68" t="n">
-        <v>7168634</v>
+        <v>7168631</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8482,10 +8482,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120416964</v>
+        <v>120417044</v>
       </c>
       <c r="B69" t="n">
-        <v>90545</v>
+        <v>79623</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8494,25 +8494,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8522,10 +8522,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>529779</v>
+        <v>529593</v>
       </c>
       <c r="R69" t="n">
-        <v>7168668</v>
+        <v>7168634</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8584,10 +8584,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120417041</v>
+        <v>120416964</v>
       </c>
       <c r="B70" t="n">
-        <v>94334</v>
+        <v>90545</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8600,21 +8600,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2809</v>
+        <v>5447</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8624,10 +8624,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>529692</v>
+        <v>529779</v>
       </c>
       <c r="R70" t="n">
-        <v>7168631</v>
+        <v>7168668</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
